--- a/responses.xlsx
+++ b/responses.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FD20"/>
+  <dimension ref="A1:HA21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1215,6 +1215,251 @@
       <c r="FD1" t="inlineStr">
         <is>
           <t>investigator_entry_note</t>
+        </is>
+      </c>
+      <c r="FE1" t="inlineStr">
+        <is>
+          <t>study_datetime</t>
+        </is>
+      </c>
+      <c r="FF1" t="inlineStr">
+        <is>
+          <t>height_cms</t>
+        </is>
+      </c>
+      <c r="FG1" t="inlineStr">
+        <is>
+          <t>weight_kgs</t>
+        </is>
+      </c>
+      <c r="FH1" t="inlineStr">
+        <is>
+          <t>age_full</t>
+        </is>
+      </c>
+      <c r="FI1" t="inlineStr">
+        <is>
+          <t>age_calculated_at</t>
+        </is>
+      </c>
+      <c r="FJ1" t="inlineStr">
+        <is>
+          <t>religion_other</t>
+        </is>
+      </c>
+      <c r="FK1" t="inlineStr">
+        <is>
+          <t>prev_hb_result</t>
+        </is>
+      </c>
+      <c r="FL1" t="inlineStr">
+        <is>
+          <t>prev_hb_device_other</t>
+        </is>
+      </c>
+      <c r="FM1" t="inlineStr">
+        <is>
+          <t>m_feas_28_a</t>
+        </is>
+      </c>
+      <c r="FN1" t="inlineStr">
+        <is>
+          <t>m_feas_28_b</t>
+        </is>
+      </c>
+      <c r="FO1" t="inlineStr">
+        <is>
+          <t>m_feas_29_a</t>
+        </is>
+      </c>
+      <c r="FP1" t="inlineStr">
+        <is>
+          <t>m_feas_29_b</t>
+        </is>
+      </c>
+      <c r="FQ1" t="inlineStr">
+        <is>
+          <t>m_feas_30_a</t>
+        </is>
+      </c>
+      <c r="FR1" t="inlineStr">
+        <is>
+          <t>m_feas_30_b</t>
+        </is>
+      </c>
+      <c r="FS1" t="inlineStr">
+        <is>
+          <t>m_feas_31_a</t>
+        </is>
+      </c>
+      <c r="FT1" t="inlineStr">
+        <is>
+          <t>m_feas_31_b</t>
+        </is>
+      </c>
+      <c r="FU1" t="inlineStr">
+        <is>
+          <t>m_feas_31_c</t>
+        </is>
+      </c>
+      <c r="FV1" t="inlineStr">
+        <is>
+          <t>m_feas_32_a</t>
+        </is>
+      </c>
+      <c r="FW1" t="inlineStr">
+        <is>
+          <t>m_feas_32_b</t>
+        </is>
+      </c>
+      <c r="FX1" t="inlineStr">
+        <is>
+          <t>m_feas_33_a</t>
+        </is>
+      </c>
+      <c r="FY1" t="inlineStr">
+        <is>
+          <t>m_feas_33_b</t>
+        </is>
+      </c>
+      <c r="FZ1" t="inlineStr">
+        <is>
+          <t>m_feas_34_a</t>
+        </is>
+      </c>
+      <c r="GA1" t="inlineStr">
+        <is>
+          <t>m_feas_34_b</t>
+        </is>
+      </c>
+      <c r="GB1" t="inlineStr">
+        <is>
+          <t>m_feas_35_a</t>
+        </is>
+      </c>
+      <c r="GC1" t="inlineStr">
+        <is>
+          <t>m_feas_35_b</t>
+        </is>
+      </c>
+      <c r="GD1" t="inlineStr">
+        <is>
+          <t>m_feas_36_a</t>
+        </is>
+      </c>
+      <c r="GE1" t="inlineStr">
+        <is>
+          <t>m_feas_36_b</t>
+        </is>
+      </c>
+      <c r="GF1" t="inlineStr">
+        <is>
+          <t>m_feas_37_a</t>
+        </is>
+      </c>
+      <c r="GG1" t="inlineStr">
+        <is>
+          <t>m_feas_37_b</t>
+        </is>
+      </c>
+      <c r="GH1" t="inlineStr">
+        <is>
+          <t>m_feas_37_c</t>
+        </is>
+      </c>
+      <c r="GI1" t="inlineStr">
+        <is>
+          <t>m_feas_37_d</t>
+        </is>
+      </c>
+      <c r="GJ1" t="inlineStr">
+        <is>
+          <t>m_feas_38_a</t>
+        </is>
+      </c>
+      <c r="GK1" t="inlineStr">
+        <is>
+          <t>m_feas_38_b</t>
+        </is>
+      </c>
+      <c r="GL1" t="inlineStr">
+        <is>
+          <t>poc_feas_44_a</t>
+        </is>
+      </c>
+      <c r="GM1" t="inlineStr">
+        <is>
+          <t>poc_feas_47_c</t>
+        </is>
+      </c>
+      <c r="GN1" t="inlineStr">
+        <is>
+          <t>poc_overall_feas</t>
+        </is>
+      </c>
+      <c r="GO1" t="inlineStr">
+        <is>
+          <t>lab_feas_60_a</t>
+        </is>
+      </c>
+      <c r="GP1" t="inlineStr">
+        <is>
+          <t>lab_feas_63_c</t>
+        </is>
+      </c>
+      <c r="GQ1" t="inlineStr">
+        <is>
+          <t>lab_overall_feas</t>
+        </is>
+      </c>
+      <c r="GR1" t="inlineStr">
+        <is>
+          <t>parent_q_73</t>
+        </is>
+      </c>
+      <c r="GS1" t="inlineStr">
+        <is>
+          <t>parent_q_74</t>
+        </is>
+      </c>
+      <c r="GT1" t="inlineStr">
+        <is>
+          <t>parent_q_75</t>
+        </is>
+      </c>
+      <c r="GU1" t="inlineStr">
+        <is>
+          <t>parent_q_76</t>
+        </is>
+      </c>
+      <c r="GV1" t="inlineStr">
+        <is>
+          <t>parent_q_77</t>
+        </is>
+      </c>
+      <c r="GW1" t="inlineStr">
+        <is>
+          <t>parent_q_78</t>
+        </is>
+      </c>
+      <c r="GX1" t="inlineStr">
+        <is>
+          <t>parent_q_79</t>
+        </is>
+      </c>
+      <c r="GY1" t="inlineStr">
+        <is>
+          <t>parent_q_80</t>
+        </is>
+      </c>
+      <c r="GZ1" t="inlineStr">
+        <is>
+          <t>parent_q_81</t>
+        </is>
+      </c>
+      <c r="HA1" t="inlineStr">
+        <is>
+          <t>referral_other</t>
         </is>
       </c>
     </row>
@@ -1391,6 +1636,55 @@
       <c r="FB2" t="inlineStr"/>
       <c r="FC2" t="inlineStr"/>
       <c r="FD2" t="inlineStr"/>
+      <c r="FE2" t="inlineStr"/>
+      <c r="FF2" t="inlineStr"/>
+      <c r="FG2" t="inlineStr"/>
+      <c r="FH2" t="inlineStr"/>
+      <c r="FI2" t="inlineStr"/>
+      <c r="FJ2" t="inlineStr"/>
+      <c r="FK2" t="inlineStr"/>
+      <c r="FL2" t="inlineStr"/>
+      <c r="FM2" t="inlineStr"/>
+      <c r="FN2" t="inlineStr"/>
+      <c r="FO2" t="inlineStr"/>
+      <c r="FP2" t="inlineStr"/>
+      <c r="FQ2" t="inlineStr"/>
+      <c r="FR2" t="inlineStr"/>
+      <c r="FS2" t="inlineStr"/>
+      <c r="FT2" t="inlineStr"/>
+      <c r="FU2" t="inlineStr"/>
+      <c r="FV2" t="inlineStr"/>
+      <c r="FW2" t="inlineStr"/>
+      <c r="FX2" t="inlineStr"/>
+      <c r="FY2" t="inlineStr"/>
+      <c r="FZ2" t="inlineStr"/>
+      <c r="GA2" t="inlineStr"/>
+      <c r="GB2" t="inlineStr"/>
+      <c r="GC2" t="inlineStr"/>
+      <c r="GD2" t="inlineStr"/>
+      <c r="GE2" t="inlineStr"/>
+      <c r="GF2" t="inlineStr"/>
+      <c r="GG2" t="inlineStr"/>
+      <c r="GH2" t="inlineStr"/>
+      <c r="GI2" t="inlineStr"/>
+      <c r="GJ2" t="inlineStr"/>
+      <c r="GK2" t="inlineStr"/>
+      <c r="GL2" t="inlineStr"/>
+      <c r="GM2" t="inlineStr"/>
+      <c r="GN2" t="inlineStr"/>
+      <c r="GO2" t="inlineStr"/>
+      <c r="GP2" t="inlineStr"/>
+      <c r="GQ2" t="inlineStr"/>
+      <c r="GR2" t="inlineStr"/>
+      <c r="GS2" t="inlineStr"/>
+      <c r="GT2" t="inlineStr"/>
+      <c r="GU2" t="inlineStr"/>
+      <c r="GV2" t="inlineStr"/>
+      <c r="GW2" t="inlineStr"/>
+      <c r="GX2" t="inlineStr"/>
+      <c r="GY2" t="inlineStr"/>
+      <c r="GZ2" t="inlineStr"/>
+      <c r="HA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1635,6 +1929,55 @@
       <c r="FB3" t="inlineStr"/>
       <c r="FC3" t="inlineStr"/>
       <c r="FD3" t="inlineStr"/>
+      <c r="FE3" t="inlineStr"/>
+      <c r="FF3" t="inlineStr"/>
+      <c r="FG3" t="inlineStr"/>
+      <c r="FH3" t="inlineStr"/>
+      <c r="FI3" t="inlineStr"/>
+      <c r="FJ3" t="inlineStr"/>
+      <c r="FK3" t="inlineStr"/>
+      <c r="FL3" t="inlineStr"/>
+      <c r="FM3" t="inlineStr"/>
+      <c r="FN3" t="inlineStr"/>
+      <c r="FO3" t="inlineStr"/>
+      <c r="FP3" t="inlineStr"/>
+      <c r="FQ3" t="inlineStr"/>
+      <c r="FR3" t="inlineStr"/>
+      <c r="FS3" t="inlineStr"/>
+      <c r="FT3" t="inlineStr"/>
+      <c r="FU3" t="inlineStr"/>
+      <c r="FV3" t="inlineStr"/>
+      <c r="FW3" t="inlineStr"/>
+      <c r="FX3" t="inlineStr"/>
+      <c r="FY3" t="inlineStr"/>
+      <c r="FZ3" t="inlineStr"/>
+      <c r="GA3" t="inlineStr"/>
+      <c r="GB3" t="inlineStr"/>
+      <c r="GC3" t="inlineStr"/>
+      <c r="GD3" t="inlineStr"/>
+      <c r="GE3" t="inlineStr"/>
+      <c r="GF3" t="inlineStr"/>
+      <c r="GG3" t="inlineStr"/>
+      <c r="GH3" t="inlineStr"/>
+      <c r="GI3" t="inlineStr"/>
+      <c r="GJ3" t="inlineStr"/>
+      <c r="GK3" t="inlineStr"/>
+      <c r="GL3" t="inlineStr"/>
+      <c r="GM3" t="inlineStr"/>
+      <c r="GN3" t="inlineStr"/>
+      <c r="GO3" t="inlineStr"/>
+      <c r="GP3" t="inlineStr"/>
+      <c r="GQ3" t="inlineStr"/>
+      <c r="GR3" t="inlineStr"/>
+      <c r="GS3" t="inlineStr"/>
+      <c r="GT3" t="inlineStr"/>
+      <c r="GU3" t="inlineStr"/>
+      <c r="GV3" t="inlineStr"/>
+      <c r="GW3" t="inlineStr"/>
+      <c r="GX3" t="inlineStr"/>
+      <c r="GY3" t="inlineStr"/>
+      <c r="GZ3" t="inlineStr"/>
+      <c r="HA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1925,6 +2268,55 @@
       <c r="FB4" t="inlineStr"/>
       <c r="FC4" t="inlineStr"/>
       <c r="FD4" t="inlineStr"/>
+      <c r="FE4" t="inlineStr"/>
+      <c r="FF4" t="inlineStr"/>
+      <c r="FG4" t="inlineStr"/>
+      <c r="FH4" t="inlineStr"/>
+      <c r="FI4" t="inlineStr"/>
+      <c r="FJ4" t="inlineStr"/>
+      <c r="FK4" t="inlineStr"/>
+      <c r="FL4" t="inlineStr"/>
+      <c r="FM4" t="inlineStr"/>
+      <c r="FN4" t="inlineStr"/>
+      <c r="FO4" t="inlineStr"/>
+      <c r="FP4" t="inlineStr"/>
+      <c r="FQ4" t="inlineStr"/>
+      <c r="FR4" t="inlineStr"/>
+      <c r="FS4" t="inlineStr"/>
+      <c r="FT4" t="inlineStr"/>
+      <c r="FU4" t="inlineStr"/>
+      <c r="FV4" t="inlineStr"/>
+      <c r="FW4" t="inlineStr"/>
+      <c r="FX4" t="inlineStr"/>
+      <c r="FY4" t="inlineStr"/>
+      <c r="FZ4" t="inlineStr"/>
+      <c r="GA4" t="inlineStr"/>
+      <c r="GB4" t="inlineStr"/>
+      <c r="GC4" t="inlineStr"/>
+      <c r="GD4" t="inlineStr"/>
+      <c r="GE4" t="inlineStr"/>
+      <c r="GF4" t="inlineStr"/>
+      <c r="GG4" t="inlineStr"/>
+      <c r="GH4" t="inlineStr"/>
+      <c r="GI4" t="inlineStr"/>
+      <c r="GJ4" t="inlineStr"/>
+      <c r="GK4" t="inlineStr"/>
+      <c r="GL4" t="inlineStr"/>
+      <c r="GM4" t="inlineStr"/>
+      <c r="GN4" t="inlineStr"/>
+      <c r="GO4" t="inlineStr"/>
+      <c r="GP4" t="inlineStr"/>
+      <c r="GQ4" t="inlineStr"/>
+      <c r="GR4" t="inlineStr"/>
+      <c r="GS4" t="inlineStr"/>
+      <c r="GT4" t="inlineStr"/>
+      <c r="GU4" t="inlineStr"/>
+      <c r="GV4" t="inlineStr"/>
+      <c r="GW4" t="inlineStr"/>
+      <c r="GX4" t="inlineStr"/>
+      <c r="GY4" t="inlineStr"/>
+      <c r="GZ4" t="inlineStr"/>
+      <c r="HA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2399,6 +2791,55 @@
       <c r="FB5" t="inlineStr"/>
       <c r="FC5" t="inlineStr"/>
       <c r="FD5" t="inlineStr"/>
+      <c r="FE5" t="inlineStr"/>
+      <c r="FF5" t="inlineStr"/>
+      <c r="FG5" t="inlineStr"/>
+      <c r="FH5" t="inlineStr"/>
+      <c r="FI5" t="inlineStr"/>
+      <c r="FJ5" t="inlineStr"/>
+      <c r="FK5" t="inlineStr"/>
+      <c r="FL5" t="inlineStr"/>
+      <c r="FM5" t="inlineStr"/>
+      <c r="FN5" t="inlineStr"/>
+      <c r="FO5" t="inlineStr"/>
+      <c r="FP5" t="inlineStr"/>
+      <c r="FQ5" t="inlineStr"/>
+      <c r="FR5" t="inlineStr"/>
+      <c r="FS5" t="inlineStr"/>
+      <c r="FT5" t="inlineStr"/>
+      <c r="FU5" t="inlineStr"/>
+      <c r="FV5" t="inlineStr"/>
+      <c r="FW5" t="inlineStr"/>
+      <c r="FX5" t="inlineStr"/>
+      <c r="FY5" t="inlineStr"/>
+      <c r="FZ5" t="inlineStr"/>
+      <c r="GA5" t="inlineStr"/>
+      <c r="GB5" t="inlineStr"/>
+      <c r="GC5" t="inlineStr"/>
+      <c r="GD5" t="inlineStr"/>
+      <c r="GE5" t="inlineStr"/>
+      <c r="GF5" t="inlineStr"/>
+      <c r="GG5" t="inlineStr"/>
+      <c r="GH5" t="inlineStr"/>
+      <c r="GI5" t="inlineStr"/>
+      <c r="GJ5" t="inlineStr"/>
+      <c r="GK5" t="inlineStr"/>
+      <c r="GL5" t="inlineStr"/>
+      <c r="GM5" t="inlineStr"/>
+      <c r="GN5" t="inlineStr"/>
+      <c r="GO5" t="inlineStr"/>
+      <c r="GP5" t="inlineStr"/>
+      <c r="GQ5" t="inlineStr"/>
+      <c r="GR5" t="inlineStr"/>
+      <c r="GS5" t="inlineStr"/>
+      <c r="GT5" t="inlineStr"/>
+      <c r="GU5" t="inlineStr"/>
+      <c r="GV5" t="inlineStr"/>
+      <c r="GW5" t="inlineStr"/>
+      <c r="GX5" t="inlineStr"/>
+      <c r="GY5" t="inlineStr"/>
+      <c r="GZ5" t="inlineStr"/>
+      <c r="HA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2883,6 +3324,55 @@
       <c r="FB6" t="inlineStr"/>
       <c r="FC6" t="inlineStr"/>
       <c r="FD6" t="inlineStr"/>
+      <c r="FE6" t="inlineStr"/>
+      <c r="FF6" t="inlineStr"/>
+      <c r="FG6" t="inlineStr"/>
+      <c r="FH6" t="inlineStr"/>
+      <c r="FI6" t="inlineStr"/>
+      <c r="FJ6" t="inlineStr"/>
+      <c r="FK6" t="inlineStr"/>
+      <c r="FL6" t="inlineStr"/>
+      <c r="FM6" t="inlineStr"/>
+      <c r="FN6" t="inlineStr"/>
+      <c r="FO6" t="inlineStr"/>
+      <c r="FP6" t="inlineStr"/>
+      <c r="FQ6" t="inlineStr"/>
+      <c r="FR6" t="inlineStr"/>
+      <c r="FS6" t="inlineStr"/>
+      <c r="FT6" t="inlineStr"/>
+      <c r="FU6" t="inlineStr"/>
+      <c r="FV6" t="inlineStr"/>
+      <c r="FW6" t="inlineStr"/>
+      <c r="FX6" t="inlineStr"/>
+      <c r="FY6" t="inlineStr"/>
+      <c r="FZ6" t="inlineStr"/>
+      <c r="GA6" t="inlineStr"/>
+      <c r="GB6" t="inlineStr"/>
+      <c r="GC6" t="inlineStr"/>
+      <c r="GD6" t="inlineStr"/>
+      <c r="GE6" t="inlineStr"/>
+      <c r="GF6" t="inlineStr"/>
+      <c r="GG6" t="inlineStr"/>
+      <c r="GH6" t="inlineStr"/>
+      <c r="GI6" t="inlineStr"/>
+      <c r="GJ6" t="inlineStr"/>
+      <c r="GK6" t="inlineStr"/>
+      <c r="GL6" t="inlineStr"/>
+      <c r="GM6" t="inlineStr"/>
+      <c r="GN6" t="inlineStr"/>
+      <c r="GO6" t="inlineStr"/>
+      <c r="GP6" t="inlineStr"/>
+      <c r="GQ6" t="inlineStr"/>
+      <c r="GR6" t="inlineStr"/>
+      <c r="GS6" t="inlineStr"/>
+      <c r="GT6" t="inlineStr"/>
+      <c r="GU6" t="inlineStr"/>
+      <c r="GV6" t="inlineStr"/>
+      <c r="GW6" t="inlineStr"/>
+      <c r="GX6" t="inlineStr"/>
+      <c r="GY6" t="inlineStr"/>
+      <c r="GZ6" t="inlineStr"/>
+      <c r="HA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2952,8 +3442,10 @@
           <t>SC</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>7</v>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -3379,6 +3871,55 @@
       <c r="FB7" t="inlineStr"/>
       <c r="FC7" t="inlineStr"/>
       <c r="FD7" t="inlineStr"/>
+      <c r="FE7" t="inlineStr"/>
+      <c r="FF7" t="inlineStr"/>
+      <c r="FG7" t="inlineStr"/>
+      <c r="FH7" t="inlineStr"/>
+      <c r="FI7" t="inlineStr"/>
+      <c r="FJ7" t="inlineStr"/>
+      <c r="FK7" t="inlineStr"/>
+      <c r="FL7" t="inlineStr"/>
+      <c r="FM7" t="inlineStr"/>
+      <c r="FN7" t="inlineStr"/>
+      <c r="FO7" t="inlineStr"/>
+      <c r="FP7" t="inlineStr"/>
+      <c r="FQ7" t="inlineStr"/>
+      <c r="FR7" t="inlineStr"/>
+      <c r="FS7" t="inlineStr"/>
+      <c r="FT7" t="inlineStr"/>
+      <c r="FU7" t="inlineStr"/>
+      <c r="FV7" t="inlineStr"/>
+      <c r="FW7" t="inlineStr"/>
+      <c r="FX7" t="inlineStr"/>
+      <c r="FY7" t="inlineStr"/>
+      <c r="FZ7" t="inlineStr"/>
+      <c r="GA7" t="inlineStr"/>
+      <c r="GB7" t="inlineStr"/>
+      <c r="GC7" t="inlineStr"/>
+      <c r="GD7" t="inlineStr"/>
+      <c r="GE7" t="inlineStr"/>
+      <c r="GF7" t="inlineStr"/>
+      <c r="GG7" t="inlineStr"/>
+      <c r="GH7" t="inlineStr"/>
+      <c r="GI7" t="inlineStr"/>
+      <c r="GJ7" t="inlineStr"/>
+      <c r="GK7" t="inlineStr"/>
+      <c r="GL7" t="inlineStr"/>
+      <c r="GM7" t="inlineStr"/>
+      <c r="GN7" t="inlineStr"/>
+      <c r="GO7" t="inlineStr"/>
+      <c r="GP7" t="inlineStr"/>
+      <c r="GQ7" t="inlineStr"/>
+      <c r="GR7" t="inlineStr"/>
+      <c r="GS7" t="inlineStr"/>
+      <c r="GT7" t="inlineStr"/>
+      <c r="GU7" t="inlineStr"/>
+      <c r="GV7" t="inlineStr"/>
+      <c r="GW7" t="inlineStr"/>
+      <c r="GX7" t="inlineStr"/>
+      <c r="GY7" t="inlineStr"/>
+      <c r="GZ7" t="inlineStr"/>
+      <c r="HA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3448,8 +3989,10 @@
           <t>SC</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>7</v>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -3863,6 +4406,55 @@
       <c r="FB8" t="inlineStr"/>
       <c r="FC8" t="inlineStr"/>
       <c r="FD8" t="inlineStr"/>
+      <c r="FE8" t="inlineStr"/>
+      <c r="FF8" t="inlineStr"/>
+      <c r="FG8" t="inlineStr"/>
+      <c r="FH8" t="inlineStr"/>
+      <c r="FI8" t="inlineStr"/>
+      <c r="FJ8" t="inlineStr"/>
+      <c r="FK8" t="inlineStr"/>
+      <c r="FL8" t="inlineStr"/>
+      <c r="FM8" t="inlineStr"/>
+      <c r="FN8" t="inlineStr"/>
+      <c r="FO8" t="inlineStr"/>
+      <c r="FP8" t="inlineStr"/>
+      <c r="FQ8" t="inlineStr"/>
+      <c r="FR8" t="inlineStr"/>
+      <c r="FS8" t="inlineStr"/>
+      <c r="FT8" t="inlineStr"/>
+      <c r="FU8" t="inlineStr"/>
+      <c r="FV8" t="inlineStr"/>
+      <c r="FW8" t="inlineStr"/>
+      <c r="FX8" t="inlineStr"/>
+      <c r="FY8" t="inlineStr"/>
+      <c r="FZ8" t="inlineStr"/>
+      <c r="GA8" t="inlineStr"/>
+      <c r="GB8" t="inlineStr"/>
+      <c r="GC8" t="inlineStr"/>
+      <c r="GD8" t="inlineStr"/>
+      <c r="GE8" t="inlineStr"/>
+      <c r="GF8" t="inlineStr"/>
+      <c r="GG8" t="inlineStr"/>
+      <c r="GH8" t="inlineStr"/>
+      <c r="GI8" t="inlineStr"/>
+      <c r="GJ8" t="inlineStr"/>
+      <c r="GK8" t="inlineStr"/>
+      <c r="GL8" t="inlineStr"/>
+      <c r="GM8" t="inlineStr"/>
+      <c r="GN8" t="inlineStr"/>
+      <c r="GO8" t="inlineStr"/>
+      <c r="GP8" t="inlineStr"/>
+      <c r="GQ8" t="inlineStr"/>
+      <c r="GR8" t="inlineStr"/>
+      <c r="GS8" t="inlineStr"/>
+      <c r="GT8" t="inlineStr"/>
+      <c r="GU8" t="inlineStr"/>
+      <c r="GV8" t="inlineStr"/>
+      <c r="GW8" t="inlineStr"/>
+      <c r="GX8" t="inlineStr"/>
+      <c r="GY8" t="inlineStr"/>
+      <c r="GZ8" t="inlineStr"/>
+      <c r="HA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4347,6 +4939,55 @@
       <c r="FB9" t="inlineStr"/>
       <c r="FC9" t="inlineStr"/>
       <c r="FD9" t="inlineStr"/>
+      <c r="FE9" t="inlineStr"/>
+      <c r="FF9" t="inlineStr"/>
+      <c r="FG9" t="inlineStr"/>
+      <c r="FH9" t="inlineStr"/>
+      <c r="FI9" t="inlineStr"/>
+      <c r="FJ9" t="inlineStr"/>
+      <c r="FK9" t="inlineStr"/>
+      <c r="FL9" t="inlineStr"/>
+      <c r="FM9" t="inlineStr"/>
+      <c r="FN9" t="inlineStr"/>
+      <c r="FO9" t="inlineStr"/>
+      <c r="FP9" t="inlineStr"/>
+      <c r="FQ9" t="inlineStr"/>
+      <c r="FR9" t="inlineStr"/>
+      <c r="FS9" t="inlineStr"/>
+      <c r="FT9" t="inlineStr"/>
+      <c r="FU9" t="inlineStr"/>
+      <c r="FV9" t="inlineStr"/>
+      <c r="FW9" t="inlineStr"/>
+      <c r="FX9" t="inlineStr"/>
+      <c r="FY9" t="inlineStr"/>
+      <c r="FZ9" t="inlineStr"/>
+      <c r="GA9" t="inlineStr"/>
+      <c r="GB9" t="inlineStr"/>
+      <c r="GC9" t="inlineStr"/>
+      <c r="GD9" t="inlineStr"/>
+      <c r="GE9" t="inlineStr"/>
+      <c r="GF9" t="inlineStr"/>
+      <c r="GG9" t="inlineStr"/>
+      <c r="GH9" t="inlineStr"/>
+      <c r="GI9" t="inlineStr"/>
+      <c r="GJ9" t="inlineStr"/>
+      <c r="GK9" t="inlineStr"/>
+      <c r="GL9" t="inlineStr"/>
+      <c r="GM9" t="inlineStr"/>
+      <c r="GN9" t="inlineStr"/>
+      <c r="GO9" t="inlineStr"/>
+      <c r="GP9" t="inlineStr"/>
+      <c r="GQ9" t="inlineStr"/>
+      <c r="GR9" t="inlineStr"/>
+      <c r="GS9" t="inlineStr"/>
+      <c r="GT9" t="inlineStr"/>
+      <c r="GU9" t="inlineStr"/>
+      <c r="GV9" t="inlineStr"/>
+      <c r="GW9" t="inlineStr"/>
+      <c r="GX9" t="inlineStr"/>
+      <c r="GY9" t="inlineStr"/>
+      <c r="GZ9" t="inlineStr"/>
+      <c r="HA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4819,6 +5460,55 @@
       <c r="FB10" t="inlineStr"/>
       <c r="FC10" t="inlineStr"/>
       <c r="FD10" t="inlineStr"/>
+      <c r="FE10" t="inlineStr"/>
+      <c r="FF10" t="inlineStr"/>
+      <c r="FG10" t="inlineStr"/>
+      <c r="FH10" t="inlineStr"/>
+      <c r="FI10" t="inlineStr"/>
+      <c r="FJ10" t="inlineStr"/>
+      <c r="FK10" t="inlineStr"/>
+      <c r="FL10" t="inlineStr"/>
+      <c r="FM10" t="inlineStr"/>
+      <c r="FN10" t="inlineStr"/>
+      <c r="FO10" t="inlineStr"/>
+      <c r="FP10" t="inlineStr"/>
+      <c r="FQ10" t="inlineStr"/>
+      <c r="FR10" t="inlineStr"/>
+      <c r="FS10" t="inlineStr"/>
+      <c r="FT10" t="inlineStr"/>
+      <c r="FU10" t="inlineStr"/>
+      <c r="FV10" t="inlineStr"/>
+      <c r="FW10" t="inlineStr"/>
+      <c r="FX10" t="inlineStr"/>
+      <c r="FY10" t="inlineStr"/>
+      <c r="FZ10" t="inlineStr"/>
+      <c r="GA10" t="inlineStr"/>
+      <c r="GB10" t="inlineStr"/>
+      <c r="GC10" t="inlineStr"/>
+      <c r="GD10" t="inlineStr"/>
+      <c r="GE10" t="inlineStr"/>
+      <c r="GF10" t="inlineStr"/>
+      <c r="GG10" t="inlineStr"/>
+      <c r="GH10" t="inlineStr"/>
+      <c r="GI10" t="inlineStr"/>
+      <c r="GJ10" t="inlineStr"/>
+      <c r="GK10" t="inlineStr"/>
+      <c r="GL10" t="inlineStr"/>
+      <c r="GM10" t="inlineStr"/>
+      <c r="GN10" t="inlineStr"/>
+      <c r="GO10" t="inlineStr"/>
+      <c r="GP10" t="inlineStr"/>
+      <c r="GQ10" t="inlineStr"/>
+      <c r="GR10" t="inlineStr"/>
+      <c r="GS10" t="inlineStr"/>
+      <c r="GT10" t="inlineStr"/>
+      <c r="GU10" t="inlineStr"/>
+      <c r="GV10" t="inlineStr"/>
+      <c r="GW10" t="inlineStr"/>
+      <c r="GX10" t="inlineStr"/>
+      <c r="GY10" t="inlineStr"/>
+      <c r="GZ10" t="inlineStr"/>
+      <c r="HA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5291,6 +5981,55 @@
       <c r="FB11" t="inlineStr"/>
       <c r="FC11" t="inlineStr"/>
       <c r="FD11" t="inlineStr"/>
+      <c r="FE11" t="inlineStr"/>
+      <c r="FF11" t="inlineStr"/>
+      <c r="FG11" t="inlineStr"/>
+      <c r="FH11" t="inlineStr"/>
+      <c r="FI11" t="inlineStr"/>
+      <c r="FJ11" t="inlineStr"/>
+      <c r="FK11" t="inlineStr"/>
+      <c r="FL11" t="inlineStr"/>
+      <c r="FM11" t="inlineStr"/>
+      <c r="FN11" t="inlineStr"/>
+      <c r="FO11" t="inlineStr"/>
+      <c r="FP11" t="inlineStr"/>
+      <c r="FQ11" t="inlineStr"/>
+      <c r="FR11" t="inlineStr"/>
+      <c r="FS11" t="inlineStr"/>
+      <c r="FT11" t="inlineStr"/>
+      <c r="FU11" t="inlineStr"/>
+      <c r="FV11" t="inlineStr"/>
+      <c r="FW11" t="inlineStr"/>
+      <c r="FX11" t="inlineStr"/>
+      <c r="FY11" t="inlineStr"/>
+      <c r="FZ11" t="inlineStr"/>
+      <c r="GA11" t="inlineStr"/>
+      <c r="GB11" t="inlineStr"/>
+      <c r="GC11" t="inlineStr"/>
+      <c r="GD11" t="inlineStr"/>
+      <c r="GE11" t="inlineStr"/>
+      <c r="GF11" t="inlineStr"/>
+      <c r="GG11" t="inlineStr"/>
+      <c r="GH11" t="inlineStr"/>
+      <c r="GI11" t="inlineStr"/>
+      <c r="GJ11" t="inlineStr"/>
+      <c r="GK11" t="inlineStr"/>
+      <c r="GL11" t="inlineStr"/>
+      <c r="GM11" t="inlineStr"/>
+      <c r="GN11" t="inlineStr"/>
+      <c r="GO11" t="inlineStr"/>
+      <c r="GP11" t="inlineStr"/>
+      <c r="GQ11" t="inlineStr"/>
+      <c r="GR11" t="inlineStr"/>
+      <c r="GS11" t="inlineStr"/>
+      <c r="GT11" t="inlineStr"/>
+      <c r="GU11" t="inlineStr"/>
+      <c r="GV11" t="inlineStr"/>
+      <c r="GW11" t="inlineStr"/>
+      <c r="GX11" t="inlineStr"/>
+      <c r="GY11" t="inlineStr"/>
+      <c r="GZ11" t="inlineStr"/>
+      <c r="HA11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5771,6 +6510,55 @@
       <c r="FB12" t="inlineStr"/>
       <c r="FC12" t="inlineStr"/>
       <c r="FD12" t="inlineStr"/>
+      <c r="FE12" t="inlineStr"/>
+      <c r="FF12" t="inlineStr"/>
+      <c r="FG12" t="inlineStr"/>
+      <c r="FH12" t="inlineStr"/>
+      <c r="FI12" t="inlineStr"/>
+      <c r="FJ12" t="inlineStr"/>
+      <c r="FK12" t="inlineStr"/>
+      <c r="FL12" t="inlineStr"/>
+      <c r="FM12" t="inlineStr"/>
+      <c r="FN12" t="inlineStr"/>
+      <c r="FO12" t="inlineStr"/>
+      <c r="FP12" t="inlineStr"/>
+      <c r="FQ12" t="inlineStr"/>
+      <c r="FR12" t="inlineStr"/>
+      <c r="FS12" t="inlineStr"/>
+      <c r="FT12" t="inlineStr"/>
+      <c r="FU12" t="inlineStr"/>
+      <c r="FV12" t="inlineStr"/>
+      <c r="FW12" t="inlineStr"/>
+      <c r="FX12" t="inlineStr"/>
+      <c r="FY12" t="inlineStr"/>
+      <c r="FZ12" t="inlineStr"/>
+      <c r="GA12" t="inlineStr"/>
+      <c r="GB12" t="inlineStr"/>
+      <c r="GC12" t="inlineStr"/>
+      <c r="GD12" t="inlineStr"/>
+      <c r="GE12" t="inlineStr"/>
+      <c r="GF12" t="inlineStr"/>
+      <c r="GG12" t="inlineStr"/>
+      <c r="GH12" t="inlineStr"/>
+      <c r="GI12" t="inlineStr"/>
+      <c r="GJ12" t="inlineStr"/>
+      <c r="GK12" t="inlineStr"/>
+      <c r="GL12" t="inlineStr"/>
+      <c r="GM12" t="inlineStr"/>
+      <c r="GN12" t="inlineStr"/>
+      <c r="GO12" t="inlineStr"/>
+      <c r="GP12" t="inlineStr"/>
+      <c r="GQ12" t="inlineStr"/>
+      <c r="GR12" t="inlineStr"/>
+      <c r="GS12" t="inlineStr"/>
+      <c r="GT12" t="inlineStr"/>
+      <c r="GU12" t="inlineStr"/>
+      <c r="GV12" t="inlineStr"/>
+      <c r="GW12" t="inlineStr"/>
+      <c r="GX12" t="inlineStr"/>
+      <c r="GY12" t="inlineStr"/>
+      <c r="GZ12" t="inlineStr"/>
+      <c r="HA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6243,6 +7031,55 @@
       <c r="FB13" t="inlineStr"/>
       <c r="FC13" t="inlineStr"/>
       <c r="FD13" t="inlineStr"/>
+      <c r="FE13" t="inlineStr"/>
+      <c r="FF13" t="inlineStr"/>
+      <c r="FG13" t="inlineStr"/>
+      <c r="FH13" t="inlineStr"/>
+      <c r="FI13" t="inlineStr"/>
+      <c r="FJ13" t="inlineStr"/>
+      <c r="FK13" t="inlineStr"/>
+      <c r="FL13" t="inlineStr"/>
+      <c r="FM13" t="inlineStr"/>
+      <c r="FN13" t="inlineStr"/>
+      <c r="FO13" t="inlineStr"/>
+      <c r="FP13" t="inlineStr"/>
+      <c r="FQ13" t="inlineStr"/>
+      <c r="FR13" t="inlineStr"/>
+      <c r="FS13" t="inlineStr"/>
+      <c r="FT13" t="inlineStr"/>
+      <c r="FU13" t="inlineStr"/>
+      <c r="FV13" t="inlineStr"/>
+      <c r="FW13" t="inlineStr"/>
+      <c r="FX13" t="inlineStr"/>
+      <c r="FY13" t="inlineStr"/>
+      <c r="FZ13" t="inlineStr"/>
+      <c r="GA13" t="inlineStr"/>
+      <c r="GB13" t="inlineStr"/>
+      <c r="GC13" t="inlineStr"/>
+      <c r="GD13" t="inlineStr"/>
+      <c r="GE13" t="inlineStr"/>
+      <c r="GF13" t="inlineStr"/>
+      <c r="GG13" t="inlineStr"/>
+      <c r="GH13" t="inlineStr"/>
+      <c r="GI13" t="inlineStr"/>
+      <c r="GJ13" t="inlineStr"/>
+      <c r="GK13" t="inlineStr"/>
+      <c r="GL13" t="inlineStr"/>
+      <c r="GM13" t="inlineStr"/>
+      <c r="GN13" t="inlineStr"/>
+      <c r="GO13" t="inlineStr"/>
+      <c r="GP13" t="inlineStr"/>
+      <c r="GQ13" t="inlineStr"/>
+      <c r="GR13" t="inlineStr"/>
+      <c r="GS13" t="inlineStr"/>
+      <c r="GT13" t="inlineStr"/>
+      <c r="GU13" t="inlineStr"/>
+      <c r="GV13" t="inlineStr"/>
+      <c r="GW13" t="inlineStr"/>
+      <c r="GX13" t="inlineStr"/>
+      <c r="GY13" t="inlineStr"/>
+      <c r="GZ13" t="inlineStr"/>
+      <c r="HA13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6723,6 +7560,55 @@
       <c r="FB14" t="inlineStr"/>
       <c r="FC14" t="inlineStr"/>
       <c r="FD14" t="inlineStr"/>
+      <c r="FE14" t="inlineStr"/>
+      <c r="FF14" t="inlineStr"/>
+      <c r="FG14" t="inlineStr"/>
+      <c r="FH14" t="inlineStr"/>
+      <c r="FI14" t="inlineStr"/>
+      <c r="FJ14" t="inlineStr"/>
+      <c r="FK14" t="inlineStr"/>
+      <c r="FL14" t="inlineStr"/>
+      <c r="FM14" t="inlineStr"/>
+      <c r="FN14" t="inlineStr"/>
+      <c r="FO14" t="inlineStr"/>
+      <c r="FP14" t="inlineStr"/>
+      <c r="FQ14" t="inlineStr"/>
+      <c r="FR14" t="inlineStr"/>
+      <c r="FS14" t="inlineStr"/>
+      <c r="FT14" t="inlineStr"/>
+      <c r="FU14" t="inlineStr"/>
+      <c r="FV14" t="inlineStr"/>
+      <c r="FW14" t="inlineStr"/>
+      <c r="FX14" t="inlineStr"/>
+      <c r="FY14" t="inlineStr"/>
+      <c r="FZ14" t="inlineStr"/>
+      <c r="GA14" t="inlineStr"/>
+      <c r="GB14" t="inlineStr"/>
+      <c r="GC14" t="inlineStr"/>
+      <c r="GD14" t="inlineStr"/>
+      <c r="GE14" t="inlineStr"/>
+      <c r="GF14" t="inlineStr"/>
+      <c r="GG14" t="inlineStr"/>
+      <c r="GH14" t="inlineStr"/>
+      <c r="GI14" t="inlineStr"/>
+      <c r="GJ14" t="inlineStr"/>
+      <c r="GK14" t="inlineStr"/>
+      <c r="GL14" t="inlineStr"/>
+      <c r="GM14" t="inlineStr"/>
+      <c r="GN14" t="inlineStr"/>
+      <c r="GO14" t="inlineStr"/>
+      <c r="GP14" t="inlineStr"/>
+      <c r="GQ14" t="inlineStr"/>
+      <c r="GR14" t="inlineStr"/>
+      <c r="GS14" t="inlineStr"/>
+      <c r="GT14" t="inlineStr"/>
+      <c r="GU14" t="inlineStr"/>
+      <c r="GV14" t="inlineStr"/>
+      <c r="GW14" t="inlineStr"/>
+      <c r="GX14" t="inlineStr"/>
+      <c r="GY14" t="inlineStr"/>
+      <c r="GZ14" t="inlineStr"/>
+      <c r="HA14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7199,6 +8085,55 @@
       <c r="FB15" t="inlineStr"/>
       <c r="FC15" t="inlineStr"/>
       <c r="FD15" t="inlineStr"/>
+      <c r="FE15" t="inlineStr"/>
+      <c r="FF15" t="inlineStr"/>
+      <c r="FG15" t="inlineStr"/>
+      <c r="FH15" t="inlineStr"/>
+      <c r="FI15" t="inlineStr"/>
+      <c r="FJ15" t="inlineStr"/>
+      <c r="FK15" t="inlineStr"/>
+      <c r="FL15" t="inlineStr"/>
+      <c r="FM15" t="inlineStr"/>
+      <c r="FN15" t="inlineStr"/>
+      <c r="FO15" t="inlineStr"/>
+      <c r="FP15" t="inlineStr"/>
+      <c r="FQ15" t="inlineStr"/>
+      <c r="FR15" t="inlineStr"/>
+      <c r="FS15" t="inlineStr"/>
+      <c r="FT15" t="inlineStr"/>
+      <c r="FU15" t="inlineStr"/>
+      <c r="FV15" t="inlineStr"/>
+      <c r="FW15" t="inlineStr"/>
+      <c r="FX15" t="inlineStr"/>
+      <c r="FY15" t="inlineStr"/>
+      <c r="FZ15" t="inlineStr"/>
+      <c r="GA15" t="inlineStr"/>
+      <c r="GB15" t="inlineStr"/>
+      <c r="GC15" t="inlineStr"/>
+      <c r="GD15" t="inlineStr"/>
+      <c r="GE15" t="inlineStr"/>
+      <c r="GF15" t="inlineStr"/>
+      <c r="GG15" t="inlineStr"/>
+      <c r="GH15" t="inlineStr"/>
+      <c r="GI15" t="inlineStr"/>
+      <c r="GJ15" t="inlineStr"/>
+      <c r="GK15" t="inlineStr"/>
+      <c r="GL15" t="inlineStr"/>
+      <c r="GM15" t="inlineStr"/>
+      <c r="GN15" t="inlineStr"/>
+      <c r="GO15" t="inlineStr"/>
+      <c r="GP15" t="inlineStr"/>
+      <c r="GQ15" t="inlineStr"/>
+      <c r="GR15" t="inlineStr"/>
+      <c r="GS15" t="inlineStr"/>
+      <c r="GT15" t="inlineStr"/>
+      <c r="GU15" t="inlineStr"/>
+      <c r="GV15" t="inlineStr"/>
+      <c r="GW15" t="inlineStr"/>
+      <c r="GX15" t="inlineStr"/>
+      <c r="GY15" t="inlineStr"/>
+      <c r="GZ15" t="inlineStr"/>
+      <c r="HA15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7683,6 +8618,55 @@
         </is>
       </c>
       <c r="FD16" t="inlineStr"/>
+      <c r="FE16" t="inlineStr"/>
+      <c r="FF16" t="inlineStr"/>
+      <c r="FG16" t="inlineStr"/>
+      <c r="FH16" t="inlineStr"/>
+      <c r="FI16" t="inlineStr"/>
+      <c r="FJ16" t="inlineStr"/>
+      <c r="FK16" t="inlineStr"/>
+      <c r="FL16" t="inlineStr"/>
+      <c r="FM16" t="inlineStr"/>
+      <c r="FN16" t="inlineStr"/>
+      <c r="FO16" t="inlineStr"/>
+      <c r="FP16" t="inlineStr"/>
+      <c r="FQ16" t="inlineStr"/>
+      <c r="FR16" t="inlineStr"/>
+      <c r="FS16" t="inlineStr"/>
+      <c r="FT16" t="inlineStr"/>
+      <c r="FU16" t="inlineStr"/>
+      <c r="FV16" t="inlineStr"/>
+      <c r="FW16" t="inlineStr"/>
+      <c r="FX16" t="inlineStr"/>
+      <c r="FY16" t="inlineStr"/>
+      <c r="FZ16" t="inlineStr"/>
+      <c r="GA16" t="inlineStr"/>
+      <c r="GB16" t="inlineStr"/>
+      <c r="GC16" t="inlineStr"/>
+      <c r="GD16" t="inlineStr"/>
+      <c r="GE16" t="inlineStr"/>
+      <c r="GF16" t="inlineStr"/>
+      <c r="GG16" t="inlineStr"/>
+      <c r="GH16" t="inlineStr"/>
+      <c r="GI16" t="inlineStr"/>
+      <c r="GJ16" t="inlineStr"/>
+      <c r="GK16" t="inlineStr"/>
+      <c r="GL16" t="inlineStr"/>
+      <c r="GM16" t="inlineStr"/>
+      <c r="GN16" t="inlineStr"/>
+      <c r="GO16" t="inlineStr"/>
+      <c r="GP16" t="inlineStr"/>
+      <c r="GQ16" t="inlineStr"/>
+      <c r="GR16" t="inlineStr"/>
+      <c r="GS16" t="inlineStr"/>
+      <c r="GT16" t="inlineStr"/>
+      <c r="GU16" t="inlineStr"/>
+      <c r="GV16" t="inlineStr"/>
+      <c r="GW16" t="inlineStr"/>
+      <c r="GX16" t="inlineStr"/>
+      <c r="GY16" t="inlineStr"/>
+      <c r="GZ16" t="inlineStr"/>
+      <c r="HA16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8163,6 +9147,55 @@
         </is>
       </c>
       <c r="FD17" t="inlineStr"/>
+      <c r="FE17" t="inlineStr"/>
+      <c r="FF17" t="inlineStr"/>
+      <c r="FG17" t="inlineStr"/>
+      <c r="FH17" t="inlineStr"/>
+      <c r="FI17" t="inlineStr"/>
+      <c r="FJ17" t="inlineStr"/>
+      <c r="FK17" t="inlineStr"/>
+      <c r="FL17" t="inlineStr"/>
+      <c r="FM17" t="inlineStr"/>
+      <c r="FN17" t="inlineStr"/>
+      <c r="FO17" t="inlineStr"/>
+      <c r="FP17" t="inlineStr"/>
+      <c r="FQ17" t="inlineStr"/>
+      <c r="FR17" t="inlineStr"/>
+      <c r="FS17" t="inlineStr"/>
+      <c r="FT17" t="inlineStr"/>
+      <c r="FU17" t="inlineStr"/>
+      <c r="FV17" t="inlineStr"/>
+      <c r="FW17" t="inlineStr"/>
+      <c r="FX17" t="inlineStr"/>
+      <c r="FY17" t="inlineStr"/>
+      <c r="FZ17" t="inlineStr"/>
+      <c r="GA17" t="inlineStr"/>
+      <c r="GB17" t="inlineStr"/>
+      <c r="GC17" t="inlineStr"/>
+      <c r="GD17" t="inlineStr"/>
+      <c r="GE17" t="inlineStr"/>
+      <c r="GF17" t="inlineStr"/>
+      <c r="GG17" t="inlineStr"/>
+      <c r="GH17" t="inlineStr"/>
+      <c r="GI17" t="inlineStr"/>
+      <c r="GJ17" t="inlineStr"/>
+      <c r="GK17" t="inlineStr"/>
+      <c r="GL17" t="inlineStr"/>
+      <c r="GM17" t="inlineStr"/>
+      <c r="GN17" t="inlineStr"/>
+      <c r="GO17" t="inlineStr"/>
+      <c r="GP17" t="inlineStr"/>
+      <c r="GQ17" t="inlineStr"/>
+      <c r="GR17" t="inlineStr"/>
+      <c r="GS17" t="inlineStr"/>
+      <c r="GT17" t="inlineStr"/>
+      <c r="GU17" t="inlineStr"/>
+      <c r="GV17" t="inlineStr"/>
+      <c r="GW17" t="inlineStr"/>
+      <c r="GX17" t="inlineStr"/>
+      <c r="GY17" t="inlineStr"/>
+      <c r="GZ17" t="inlineStr"/>
+      <c r="HA17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8647,6 +9680,55 @@
         </is>
       </c>
       <c r="FD18" t="inlineStr"/>
+      <c r="FE18" t="inlineStr"/>
+      <c r="FF18" t="inlineStr"/>
+      <c r="FG18" t="inlineStr"/>
+      <c r="FH18" t="inlineStr"/>
+      <c r="FI18" t="inlineStr"/>
+      <c r="FJ18" t="inlineStr"/>
+      <c r="FK18" t="inlineStr"/>
+      <c r="FL18" t="inlineStr"/>
+      <c r="FM18" t="inlineStr"/>
+      <c r="FN18" t="inlineStr"/>
+      <c r="FO18" t="inlineStr"/>
+      <c r="FP18" t="inlineStr"/>
+      <c r="FQ18" t="inlineStr"/>
+      <c r="FR18" t="inlineStr"/>
+      <c r="FS18" t="inlineStr"/>
+      <c r="FT18" t="inlineStr"/>
+      <c r="FU18" t="inlineStr"/>
+      <c r="FV18" t="inlineStr"/>
+      <c r="FW18" t="inlineStr"/>
+      <c r="FX18" t="inlineStr"/>
+      <c r="FY18" t="inlineStr"/>
+      <c r="FZ18" t="inlineStr"/>
+      <c r="GA18" t="inlineStr"/>
+      <c r="GB18" t="inlineStr"/>
+      <c r="GC18" t="inlineStr"/>
+      <c r="GD18" t="inlineStr"/>
+      <c r="GE18" t="inlineStr"/>
+      <c r="GF18" t="inlineStr"/>
+      <c r="GG18" t="inlineStr"/>
+      <c r="GH18" t="inlineStr"/>
+      <c r="GI18" t="inlineStr"/>
+      <c r="GJ18" t="inlineStr"/>
+      <c r="GK18" t="inlineStr"/>
+      <c r="GL18" t="inlineStr"/>
+      <c r="GM18" t="inlineStr"/>
+      <c r="GN18" t="inlineStr"/>
+      <c r="GO18" t="inlineStr"/>
+      <c r="GP18" t="inlineStr"/>
+      <c r="GQ18" t="inlineStr"/>
+      <c r="GR18" t="inlineStr"/>
+      <c r="GS18" t="inlineStr"/>
+      <c r="GT18" t="inlineStr"/>
+      <c r="GU18" t="inlineStr"/>
+      <c r="GV18" t="inlineStr"/>
+      <c r="GW18" t="inlineStr"/>
+      <c r="GX18" t="inlineStr"/>
+      <c r="GY18" t="inlineStr"/>
+      <c r="GZ18" t="inlineStr"/>
+      <c r="HA18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9131,6 +10213,55 @@
         </is>
       </c>
       <c r="FD19" t="inlineStr"/>
+      <c r="FE19" t="inlineStr"/>
+      <c r="FF19" t="inlineStr"/>
+      <c r="FG19" t="inlineStr"/>
+      <c r="FH19" t="inlineStr"/>
+      <c r="FI19" t="inlineStr"/>
+      <c r="FJ19" t="inlineStr"/>
+      <c r="FK19" t="inlineStr"/>
+      <c r="FL19" t="inlineStr"/>
+      <c r="FM19" t="inlineStr"/>
+      <c r="FN19" t="inlineStr"/>
+      <c r="FO19" t="inlineStr"/>
+      <c r="FP19" t="inlineStr"/>
+      <c r="FQ19" t="inlineStr"/>
+      <c r="FR19" t="inlineStr"/>
+      <c r="FS19" t="inlineStr"/>
+      <c r="FT19" t="inlineStr"/>
+      <c r="FU19" t="inlineStr"/>
+      <c r="FV19" t="inlineStr"/>
+      <c r="FW19" t="inlineStr"/>
+      <c r="FX19" t="inlineStr"/>
+      <c r="FY19" t="inlineStr"/>
+      <c r="FZ19" t="inlineStr"/>
+      <c r="GA19" t="inlineStr"/>
+      <c r="GB19" t="inlineStr"/>
+      <c r="GC19" t="inlineStr"/>
+      <c r="GD19" t="inlineStr"/>
+      <c r="GE19" t="inlineStr"/>
+      <c r="GF19" t="inlineStr"/>
+      <c r="GG19" t="inlineStr"/>
+      <c r="GH19" t="inlineStr"/>
+      <c r="GI19" t="inlineStr"/>
+      <c r="GJ19" t="inlineStr"/>
+      <c r="GK19" t="inlineStr"/>
+      <c r="GL19" t="inlineStr"/>
+      <c r="GM19" t="inlineStr"/>
+      <c r="GN19" t="inlineStr"/>
+      <c r="GO19" t="inlineStr"/>
+      <c r="GP19" t="inlineStr"/>
+      <c r="GQ19" t="inlineStr"/>
+      <c r="GR19" t="inlineStr"/>
+      <c r="GS19" t="inlineStr"/>
+      <c r="GT19" t="inlineStr"/>
+      <c r="GU19" t="inlineStr"/>
+      <c r="GV19" t="inlineStr"/>
+      <c r="GW19" t="inlineStr"/>
+      <c r="GX19" t="inlineStr"/>
+      <c r="GY19" t="inlineStr"/>
+      <c r="GZ19" t="inlineStr"/>
+      <c r="HA19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9615,6 +10746,526 @@
         </is>
       </c>
       <c r="FD20" t="inlineStr"/>
+      <c r="FE20" t="inlineStr"/>
+      <c r="FF20" t="inlineStr"/>
+      <c r="FG20" t="inlineStr"/>
+      <c r="FH20" t="inlineStr"/>
+      <c r="FI20" t="inlineStr"/>
+      <c r="FJ20" t="inlineStr"/>
+      <c r="FK20" t="inlineStr"/>
+      <c r="FL20" t="inlineStr"/>
+      <c r="FM20" t="inlineStr"/>
+      <c r="FN20" t="inlineStr"/>
+      <c r="FO20" t="inlineStr"/>
+      <c r="FP20" t="inlineStr"/>
+      <c r="FQ20" t="inlineStr"/>
+      <c r="FR20" t="inlineStr"/>
+      <c r="FS20" t="inlineStr"/>
+      <c r="FT20" t="inlineStr"/>
+      <c r="FU20" t="inlineStr"/>
+      <c r="FV20" t="inlineStr"/>
+      <c r="FW20" t="inlineStr"/>
+      <c r="FX20" t="inlineStr"/>
+      <c r="FY20" t="inlineStr"/>
+      <c r="FZ20" t="inlineStr"/>
+      <c r="GA20" t="inlineStr"/>
+      <c r="GB20" t="inlineStr"/>
+      <c r="GC20" t="inlineStr"/>
+      <c r="GD20" t="inlineStr"/>
+      <c r="GE20" t="inlineStr"/>
+      <c r="GF20" t="inlineStr"/>
+      <c r="GG20" t="inlineStr"/>
+      <c r="GH20" t="inlineStr"/>
+      <c r="GI20" t="inlineStr"/>
+      <c r="GJ20" t="inlineStr"/>
+      <c r="GK20" t="inlineStr"/>
+      <c r="GL20" t="inlineStr"/>
+      <c r="GM20" t="inlineStr"/>
+      <c r="GN20" t="inlineStr"/>
+      <c r="GO20" t="inlineStr"/>
+      <c r="GP20" t="inlineStr"/>
+      <c r="GQ20" t="inlineStr"/>
+      <c r="GR20" t="inlineStr"/>
+      <c r="GS20" t="inlineStr"/>
+      <c r="GT20" t="inlineStr"/>
+      <c r="GU20" t="inlineStr"/>
+      <c r="GV20" t="inlineStr"/>
+      <c r="GW20" t="inlineStr"/>
+      <c r="GX20" t="inlineStr"/>
+      <c r="GY20" t="inlineStr"/>
+      <c r="GZ20" t="inlineStr"/>
+      <c r="HA20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2310f7fb-2efe-41fe-afe5-4b5a5f105ed6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>JR140722MSIH</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-03-02 22:06:22</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2022-07-14</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>JR140722MSIH</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Upper</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>JR140722MSIH</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Jahnavi</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr"/>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr"/>
+      <c r="BJ21" t="inlineStr"/>
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="inlineStr"/>
+      <c r="BM21" t="inlineStr"/>
+      <c r="BN21" t="inlineStr"/>
+      <c r="BO21" t="inlineStr"/>
+      <c r="BP21" t="inlineStr"/>
+      <c r="BQ21" t="inlineStr"/>
+      <c r="BR21" t="inlineStr"/>
+      <c r="BS21" t="inlineStr"/>
+      <c r="BT21" t="inlineStr"/>
+      <c r="BU21" t="inlineStr"/>
+      <c r="BV21" t="inlineStr"/>
+      <c r="BW21" t="inlineStr"/>
+      <c r="BX21" t="inlineStr"/>
+      <c r="BY21" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BZ21" t="inlineStr"/>
+      <c r="CA21" t="inlineStr"/>
+      <c r="CB21" t="inlineStr"/>
+      <c r="CC21" t="inlineStr"/>
+      <c r="CD21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr"/>
+      <c r="CF21" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="CG21" t="inlineStr"/>
+      <c r="CH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI21" t="inlineStr"/>
+      <c r="CJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL21" t="inlineStr"/>
+      <c r="CM21" t="inlineStr"/>
+      <c r="CN21" t="inlineStr"/>
+      <c r="CO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CQ21" t="inlineStr"/>
+      <c r="CR21" t="inlineStr"/>
+      <c r="CS21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CT21" t="inlineStr"/>
+      <c r="CU21" t="inlineStr"/>
+      <c r="CV21" t="inlineStr"/>
+      <c r="CW21" t="inlineStr"/>
+      <c r="CX21" t="inlineStr"/>
+      <c r="CY21" t="inlineStr"/>
+      <c r="CZ21" t="inlineStr"/>
+      <c r="DA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB21" t="inlineStr"/>
+      <c r="DC21" t="inlineStr"/>
+      <c r="DD21" t="inlineStr"/>
+      <c r="DE21" t="inlineStr"/>
+      <c r="DF21" t="inlineStr"/>
+      <c r="DG21" t="inlineStr"/>
+      <c r="DH21" t="inlineStr"/>
+      <c r="DI21" t="inlineStr"/>
+      <c r="DJ21" t="inlineStr"/>
+      <c r="DK21" t="inlineStr"/>
+      <c r="DL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM21" t="inlineStr"/>
+      <c r="DN21" t="inlineStr">
+        <is>
+          <t>jhon</t>
+        </is>
+      </c>
+      <c r="DO21" t="inlineStr"/>
+      <c r="DP21" t="inlineStr"/>
+      <c r="DQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS21" t="inlineStr"/>
+      <c r="DT21" t="inlineStr"/>
+      <c r="DU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV21" t="inlineStr"/>
+      <c r="DW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX21" t="inlineStr"/>
+      <c r="DY21" t="inlineStr"/>
+      <c r="DZ21" t="inlineStr"/>
+      <c r="EA21" t="inlineStr"/>
+      <c r="EB21" t="inlineStr"/>
+      <c r="EC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED21" t="inlineStr"/>
+      <c r="EE21" t="inlineStr"/>
+      <c r="EF21" t="inlineStr"/>
+      <c r="EG21" t="inlineStr"/>
+      <c r="EH21" t="inlineStr"/>
+      <c r="EI21" t="inlineStr"/>
+      <c r="EJ21" t="inlineStr"/>
+      <c r="EK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL21" t="inlineStr"/>
+      <c r="EM21" t="inlineStr">
+        <is>
+          <t>sri indu</t>
+        </is>
+      </c>
+      <c r="EN21" t="inlineStr"/>
+      <c r="EO21" t="inlineStr"/>
+      <c r="EP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER21" t="inlineStr"/>
+      <c r="ES21" t="inlineStr"/>
+      <c r="ET21" t="inlineStr"/>
+      <c r="EU21" t="inlineStr"/>
+      <c r="EV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW21" t="inlineStr"/>
+      <c r="EX21" t="inlineStr"/>
+      <c r="EY21" t="inlineStr"/>
+      <c r="EZ21" t="inlineStr"/>
+      <c r="FA21" t="inlineStr"/>
+      <c r="FB21" t="inlineStr"/>
+      <c r="FC21" t="inlineStr">
+        <is>
+          <t>Jahnavi</t>
+        </is>
+      </c>
+      <c r="FD21" t="inlineStr"/>
+      <c r="FE21" t="inlineStr">
+        <is>
+          <t>2026-03-02 22:05:50</t>
+        </is>
+      </c>
+      <c r="FF21" t="inlineStr"/>
+      <c r="FG21" t="inlineStr"/>
+      <c r="FH21" t="inlineStr">
+        <is>
+          <t>3 years 7 months 16 days</t>
+        </is>
+      </c>
+      <c r="FI21" t="inlineStr">
+        <is>
+          <t>2/3/2026, 10:05:50 pm</t>
+        </is>
+      </c>
+      <c r="FJ21" t="inlineStr"/>
+      <c r="FK21" t="inlineStr"/>
+      <c r="FL21" t="inlineStr"/>
+      <c r="FM21" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="FN21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FO21" t="inlineStr"/>
+      <c r="FP21" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="FQ21" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="FR21" t="inlineStr">
+        <is>
+          <t>Easily available</t>
+        </is>
+      </c>
+      <c r="FS21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FT21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FU21" t="inlineStr">
+        <is>
+          <t>&lt;1 min</t>
+        </is>
+      </c>
+      <c r="FV21" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="FW21" t="inlineStr">
+        <is>
+          <t>Not affected</t>
+        </is>
+      </c>
+      <c r="FX21" t="inlineStr">
+        <is>
+          <t>Highly portable</t>
+        </is>
+      </c>
+      <c r="FY21" t="inlineStr">
+        <is>
+          <t>Battery operated</t>
+        </is>
+      </c>
+      <c r="FZ21" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="GA21" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="GB21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="GC21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="GD21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="GE21" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="GF21" t="inlineStr">
+        <is>
+          <t>Very safe</t>
+        </is>
+      </c>
+      <c r="GG21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="GH21" t="inlineStr"/>
+      <c r="GI21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="GJ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="GK21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="GL21" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="GM21" t="inlineStr">
+        <is>
+          <t>&lt;1 min</t>
+        </is>
+      </c>
+      <c r="GN21" t="n">
+        <v>1</v>
+      </c>
+      <c r="GO21" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="GP21" t="inlineStr">
+        <is>
+          <t>&lt;1 min</t>
+        </is>
+      </c>
+      <c r="GQ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="GR21" t="n">
+        <v>1</v>
+      </c>
+      <c r="GS21" t="n">
+        <v>1</v>
+      </c>
+      <c r="GT21" t="n">
+        <v>1</v>
+      </c>
+      <c r="GU21" t="n">
+        <v>1</v>
+      </c>
+      <c r="GV21" t="n">
+        <v>1</v>
+      </c>
+      <c r="GW21" t="n">
+        <v>1</v>
+      </c>
+      <c r="GX21" t="n">
+        <v>1</v>
+      </c>
+      <c r="GY21" t="n">
+        <v>1</v>
+      </c>
+      <c r="GZ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="HA21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/responses.xlsx
+++ b/responses.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HA21"/>
+  <dimension ref="A1:HB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1460,6 +1460,11 @@
       <c r="HA1" t="inlineStr">
         <is>
           <t>referral_other</t>
+        </is>
+      </c>
+      <c r="HB1" t="inlineStr">
+        <is>
+          <t>_csrf_token</t>
         </is>
       </c>
     </row>
@@ -1685,6 +1690,7 @@
       <c r="GY2" t="inlineStr"/>
       <c r="GZ2" t="inlineStr"/>
       <c r="HA2" t="inlineStr"/>
+      <c r="HB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1978,6 +1984,7 @@
       <c r="GY3" t="inlineStr"/>
       <c r="GZ3" t="inlineStr"/>
       <c r="HA3" t="inlineStr"/>
+      <c r="HB3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2317,6 +2324,7 @@
       <c r="GY4" t="inlineStr"/>
       <c r="GZ4" t="inlineStr"/>
       <c r="HA4" t="inlineStr"/>
+      <c r="HB4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2840,6 +2848,7 @@
       <c r="GY5" t="inlineStr"/>
       <c r="GZ5" t="inlineStr"/>
       <c r="HA5" t="inlineStr"/>
+      <c r="HB5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3373,6 +3382,7 @@
       <c r="GY6" t="inlineStr"/>
       <c r="GZ6" t="inlineStr"/>
       <c r="HA6" t="inlineStr"/>
+      <c r="HB6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3920,6 +3930,7 @@
       <c r="GY7" t="inlineStr"/>
       <c r="GZ7" t="inlineStr"/>
       <c r="HA7" t="inlineStr"/>
+      <c r="HB7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4455,6 +4466,7 @@
       <c r="GY8" t="inlineStr"/>
       <c r="GZ8" t="inlineStr"/>
       <c r="HA8" t="inlineStr"/>
+      <c r="HB8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4988,6 +5000,7 @@
       <c r="GY9" t="inlineStr"/>
       <c r="GZ9" t="inlineStr"/>
       <c r="HA9" t="inlineStr"/>
+      <c r="HB9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5509,6 +5522,7 @@
       <c r="GY10" t="inlineStr"/>
       <c r="GZ10" t="inlineStr"/>
       <c r="HA10" t="inlineStr"/>
+      <c r="HB10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6030,6 +6044,7 @@
       <c r="GY11" t="inlineStr"/>
       <c r="GZ11" t="inlineStr"/>
       <c r="HA11" t="inlineStr"/>
+      <c r="HB11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6559,6 +6574,7 @@
       <c r="GY12" t="inlineStr"/>
       <c r="GZ12" t="inlineStr"/>
       <c r="HA12" t="inlineStr"/>
+      <c r="HB12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7080,6 +7096,7 @@
       <c r="GY13" t="inlineStr"/>
       <c r="GZ13" t="inlineStr"/>
       <c r="HA13" t="inlineStr"/>
+      <c r="HB13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7609,6 +7626,7 @@
       <c r="GY14" t="inlineStr"/>
       <c r="GZ14" t="inlineStr"/>
       <c r="HA14" t="inlineStr"/>
+      <c r="HB14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8134,6 +8152,7 @@
       <c r="GY15" t="inlineStr"/>
       <c r="GZ15" t="inlineStr"/>
       <c r="HA15" t="inlineStr"/>
+      <c r="HB15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8667,6 +8686,7 @@
       <c r="GY16" t="inlineStr"/>
       <c r="GZ16" t="inlineStr"/>
       <c r="HA16" t="inlineStr"/>
+      <c r="HB16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9196,6 +9216,7 @@
       <c r="GY17" t="inlineStr"/>
       <c r="GZ17" t="inlineStr"/>
       <c r="HA17" t="inlineStr"/>
+      <c r="HB17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9729,6 +9750,7 @@
       <c r="GY18" t="inlineStr"/>
       <c r="GZ18" t="inlineStr"/>
       <c r="HA18" t="inlineStr"/>
+      <c r="HB18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10262,6 +10284,7 @@
       <c r="GY19" t="inlineStr"/>
       <c r="GZ19" t="inlineStr"/>
       <c r="HA19" t="inlineStr"/>
+      <c r="HB19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -10795,6 +10818,7 @@
       <c r="GY20" t="inlineStr"/>
       <c r="GZ20" t="inlineStr"/>
       <c r="HA20" t="inlineStr"/>
+      <c r="HB20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11266,6 +11290,355 @@
         <v>1</v>
       </c>
       <c r="HA21" t="inlineStr"/>
+      <c r="HB21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>65a855b7-9b28-4b9b-8513-faa9f0a8f141</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LV240721MWEA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-03-05 18:02:08</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2021-07-24</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>LV240721MWEA</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Upper</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>LV240721MWEA</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Jahnavi</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>PHC</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr"/>
+      <c r="BA22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr"/>
+      <c r="BJ22" t="inlineStr"/>
+      <c r="BK22" t="inlineStr"/>
+      <c r="BL22" t="inlineStr"/>
+      <c r="BM22" t="inlineStr"/>
+      <c r="BN22" t="inlineStr"/>
+      <c r="BO22" t="inlineStr"/>
+      <c r="BP22" t="inlineStr"/>
+      <c r="BQ22" t="inlineStr"/>
+      <c r="BR22" t="inlineStr"/>
+      <c r="BS22" t="inlineStr"/>
+      <c r="BT22" t="inlineStr"/>
+      <c r="BU22" t="inlineStr"/>
+      <c r="BV22" t="inlineStr"/>
+      <c r="BW22" t="inlineStr"/>
+      <c r="BX22" t="inlineStr"/>
+      <c r="BY22" t="inlineStr"/>
+      <c r="BZ22" t="inlineStr"/>
+      <c r="CA22" t="inlineStr"/>
+      <c r="CB22" t="inlineStr"/>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL22" t="inlineStr"/>
+      <c r="CM22" t="inlineStr"/>
+      <c r="CN22" t="inlineStr"/>
+      <c r="CO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CQ22" t="inlineStr"/>
+      <c r="CR22" t="inlineStr"/>
+      <c r="CS22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CT22" t="inlineStr"/>
+      <c r="CU22" t="inlineStr"/>
+      <c r="CV22" t="inlineStr"/>
+      <c r="CW22" t="inlineStr"/>
+      <c r="CX22" t="inlineStr"/>
+      <c r="CY22" t="inlineStr"/>
+      <c r="CZ22" t="inlineStr"/>
+      <c r="DA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB22" t="inlineStr"/>
+      <c r="DC22" t="inlineStr"/>
+      <c r="DD22" t="inlineStr"/>
+      <c r="DE22" t="inlineStr"/>
+      <c r="DF22" t="inlineStr"/>
+      <c r="DG22" t="inlineStr"/>
+      <c r="DH22" t="inlineStr"/>
+      <c r="DI22" t="inlineStr"/>
+      <c r="DJ22" t="inlineStr"/>
+      <c r="DK22" t="inlineStr"/>
+      <c r="DL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM22" t="inlineStr"/>
+      <c r="DN22" t="inlineStr">
+        <is>
+          <t>leo</t>
+        </is>
+      </c>
+      <c r="DO22" t="inlineStr"/>
+      <c r="DP22" t="inlineStr"/>
+      <c r="DQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS22" t="inlineStr"/>
+      <c r="DT22" t="inlineStr"/>
+      <c r="DU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV22" t="inlineStr"/>
+      <c r="DW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX22" t="inlineStr"/>
+      <c r="DY22" t="inlineStr"/>
+      <c r="DZ22" t="inlineStr"/>
+      <c r="EA22" t="inlineStr"/>
+      <c r="EB22" t="inlineStr"/>
+      <c r="EC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED22" t="inlineStr"/>
+      <c r="EE22" t="inlineStr"/>
+      <c r="EF22" t="inlineStr"/>
+      <c r="EG22" t="inlineStr"/>
+      <c r="EH22" t="inlineStr"/>
+      <c r="EI22" t="inlineStr"/>
+      <c r="EJ22" t="inlineStr"/>
+      <c r="EK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL22" t="inlineStr"/>
+      <c r="EM22" t="inlineStr">
+        <is>
+          <t>west</t>
+        </is>
+      </c>
+      <c r="EN22" t="inlineStr"/>
+      <c r="EO22" t="inlineStr"/>
+      <c r="EP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER22" t="inlineStr"/>
+      <c r="ES22" t="inlineStr"/>
+      <c r="ET22" t="inlineStr"/>
+      <c r="EU22" t="inlineStr"/>
+      <c r="EV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW22" t="inlineStr"/>
+      <c r="EX22" t="inlineStr"/>
+      <c r="EY22" t="inlineStr"/>
+      <c r="EZ22" t="inlineStr"/>
+      <c r="FA22" t="inlineStr"/>
+      <c r="FB22" t="inlineStr"/>
+      <c r="FC22" t="inlineStr">
+        <is>
+          <t>Jahnavi</t>
+        </is>
+      </c>
+      <c r="FD22" t="inlineStr"/>
+      <c r="FE22" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:02:00+05:30</t>
+        </is>
+      </c>
+      <c r="FF22" t="inlineStr"/>
+      <c r="FG22" t="inlineStr"/>
+      <c r="FH22" t="inlineStr">
+        <is>
+          <t>4 years 7 months 9 days</t>
+        </is>
+      </c>
+      <c r="FI22" t="inlineStr">
+        <is>
+          <t>2026-03-05T18:02:00+05:30</t>
+        </is>
+      </c>
+      <c r="FJ22" t="inlineStr"/>
+      <c r="FK22" t="inlineStr"/>
+      <c r="FL22" t="inlineStr"/>
+      <c r="FM22" t="inlineStr"/>
+      <c r="FN22" t="inlineStr"/>
+      <c r="FO22" t="inlineStr"/>
+      <c r="FP22" t="inlineStr"/>
+      <c r="FQ22" t="inlineStr"/>
+      <c r="FR22" t="inlineStr"/>
+      <c r="FS22" t="inlineStr"/>
+      <c r="FT22" t="inlineStr"/>
+      <c r="FU22" t="inlineStr"/>
+      <c r="FV22" t="inlineStr"/>
+      <c r="FW22" t="inlineStr"/>
+      <c r="FX22" t="inlineStr"/>
+      <c r="FY22" t="inlineStr"/>
+      <c r="FZ22" t="inlineStr"/>
+      <c r="GA22" t="inlineStr"/>
+      <c r="GB22" t="inlineStr"/>
+      <c r="GC22" t="inlineStr"/>
+      <c r="GD22" t="inlineStr"/>
+      <c r="GE22" t="inlineStr"/>
+      <c r="GF22" t="inlineStr"/>
+      <c r="GG22" t="inlineStr"/>
+      <c r="GH22" t="inlineStr"/>
+      <c r="GI22" t="inlineStr"/>
+      <c r="GJ22" t="inlineStr"/>
+      <c r="GK22" t="inlineStr"/>
+      <c r="GL22" t="inlineStr"/>
+      <c r="GM22" t="inlineStr"/>
+      <c r="GN22" t="inlineStr"/>
+      <c r="GO22" t="inlineStr"/>
+      <c r="GP22" t="inlineStr"/>
+      <c r="GQ22" t="inlineStr"/>
+      <c r="GR22" t="inlineStr"/>
+      <c r="GS22" t="inlineStr"/>
+      <c r="GT22" t="inlineStr"/>
+      <c r="GU22" t="inlineStr"/>
+      <c r="GV22" t="inlineStr"/>
+      <c r="GW22" t="inlineStr"/>
+      <c r="GX22" t="inlineStr"/>
+      <c r="GY22" t="inlineStr"/>
+      <c r="GZ22" t="inlineStr"/>
+      <c r="HA22" t="inlineStr"/>
+      <c r="HB22" t="inlineStr">
+        <is>
+          <t>7JVBu_U7W1AEd7dyoZ37wZOeelHewzgavOCk1lZNxA4</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/responses.xlsx
+++ b/responses.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HB22"/>
+  <dimension ref="A1:HF26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1465,6 +1465,26 @@
       <c r="HB1" t="inlineStr">
         <is>
           <t>_csrf_token</t>
+        </is>
+      </c>
+      <c r="HC1" t="inlineStr">
+        <is>
+          <t>hb_previously_tested</t>
+        </is>
+      </c>
+      <c r="HD1" t="inlineStr">
+        <is>
+          <t>prev_hb_device</t>
+        </is>
+      </c>
+      <c r="HE1" t="inlineStr">
+        <is>
+          <t>device_seq</t>
+        </is>
+      </c>
+      <c r="HF1" t="inlineStr">
+        <is>
+          <t>masimo_attempts</t>
         </is>
       </c>
     </row>
@@ -1691,6 +1711,10 @@
       <c r="GZ2" t="inlineStr"/>
       <c r="HA2" t="inlineStr"/>
       <c r="HB2" t="inlineStr"/>
+      <c r="HC2" t="inlineStr"/>
+      <c r="HD2" t="inlineStr"/>
+      <c r="HE2" t="inlineStr"/>
+      <c r="HF2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1985,6 +2009,10 @@
       <c r="GZ3" t="inlineStr"/>
       <c r="HA3" t="inlineStr"/>
       <c r="HB3" t="inlineStr"/>
+      <c r="HC3" t="inlineStr"/>
+      <c r="HD3" t="inlineStr"/>
+      <c r="HE3" t="inlineStr"/>
+      <c r="HF3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2325,6 +2353,10 @@
       <c r="GZ4" t="inlineStr"/>
       <c r="HA4" t="inlineStr"/>
       <c r="HB4" t="inlineStr"/>
+      <c r="HC4" t="inlineStr"/>
+      <c r="HD4" t="inlineStr"/>
+      <c r="HE4" t="inlineStr"/>
+      <c r="HF4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2849,6 +2881,10 @@
       <c r="GZ5" t="inlineStr"/>
       <c r="HA5" t="inlineStr"/>
       <c r="HB5" t="inlineStr"/>
+      <c r="HC5" t="inlineStr"/>
+      <c r="HD5" t="inlineStr"/>
+      <c r="HE5" t="inlineStr"/>
+      <c r="HF5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3383,6 +3419,10 @@
       <c r="GZ6" t="inlineStr"/>
       <c r="HA6" t="inlineStr"/>
       <c r="HB6" t="inlineStr"/>
+      <c r="HC6" t="inlineStr"/>
+      <c r="HD6" t="inlineStr"/>
+      <c r="HE6" t="inlineStr"/>
+      <c r="HF6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3931,6 +3971,10 @@
       <c r="GZ7" t="inlineStr"/>
       <c r="HA7" t="inlineStr"/>
       <c r="HB7" t="inlineStr"/>
+      <c r="HC7" t="inlineStr"/>
+      <c r="HD7" t="inlineStr"/>
+      <c r="HE7" t="inlineStr"/>
+      <c r="HF7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4467,6 +4511,10 @@
       <c r="GZ8" t="inlineStr"/>
       <c r="HA8" t="inlineStr"/>
       <c r="HB8" t="inlineStr"/>
+      <c r="HC8" t="inlineStr"/>
+      <c r="HD8" t="inlineStr"/>
+      <c r="HE8" t="inlineStr"/>
+      <c r="HF8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5001,6 +5049,10 @@
       <c r="GZ9" t="inlineStr"/>
       <c r="HA9" t="inlineStr"/>
       <c r="HB9" t="inlineStr"/>
+      <c r="HC9" t="inlineStr"/>
+      <c r="HD9" t="inlineStr"/>
+      <c r="HE9" t="inlineStr"/>
+      <c r="HF9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5523,6 +5575,10 @@
       <c r="GZ10" t="inlineStr"/>
       <c r="HA10" t="inlineStr"/>
       <c r="HB10" t="inlineStr"/>
+      <c r="HC10" t="inlineStr"/>
+      <c r="HD10" t="inlineStr"/>
+      <c r="HE10" t="inlineStr"/>
+      <c r="HF10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6045,6 +6101,10 @@
       <c r="GZ11" t="inlineStr"/>
       <c r="HA11" t="inlineStr"/>
       <c r="HB11" t="inlineStr"/>
+      <c r="HC11" t="inlineStr"/>
+      <c r="HD11" t="inlineStr"/>
+      <c r="HE11" t="inlineStr"/>
+      <c r="HF11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6575,6 +6635,10 @@
       <c r="GZ12" t="inlineStr"/>
       <c r="HA12" t="inlineStr"/>
       <c r="HB12" t="inlineStr"/>
+      <c r="HC12" t="inlineStr"/>
+      <c r="HD12" t="inlineStr"/>
+      <c r="HE12" t="inlineStr"/>
+      <c r="HF12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7097,6 +7161,10 @@
       <c r="GZ13" t="inlineStr"/>
       <c r="HA13" t="inlineStr"/>
       <c r="HB13" t="inlineStr"/>
+      <c r="HC13" t="inlineStr"/>
+      <c r="HD13" t="inlineStr"/>
+      <c r="HE13" t="inlineStr"/>
+      <c r="HF13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7627,6 +7695,10 @@
       <c r="GZ14" t="inlineStr"/>
       <c r="HA14" t="inlineStr"/>
       <c r="HB14" t="inlineStr"/>
+      <c r="HC14" t="inlineStr"/>
+      <c r="HD14" t="inlineStr"/>
+      <c r="HE14" t="inlineStr"/>
+      <c r="HF14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8153,6 +8225,10 @@
       <c r="GZ15" t="inlineStr"/>
       <c r="HA15" t="inlineStr"/>
       <c r="HB15" t="inlineStr"/>
+      <c r="HC15" t="inlineStr"/>
+      <c r="HD15" t="inlineStr"/>
+      <c r="HE15" t="inlineStr"/>
+      <c r="HF15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8687,6 +8763,10 @@
       <c r="GZ16" t="inlineStr"/>
       <c r="HA16" t="inlineStr"/>
       <c r="HB16" t="inlineStr"/>
+      <c r="HC16" t="inlineStr"/>
+      <c r="HD16" t="inlineStr"/>
+      <c r="HE16" t="inlineStr"/>
+      <c r="HF16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9217,6 +9297,10 @@
       <c r="GZ17" t="inlineStr"/>
       <c r="HA17" t="inlineStr"/>
       <c r="HB17" t="inlineStr"/>
+      <c r="HC17" t="inlineStr"/>
+      <c r="HD17" t="inlineStr"/>
+      <c r="HE17" t="inlineStr"/>
+      <c r="HF17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9751,6 +9835,10 @@
       <c r="GZ18" t="inlineStr"/>
       <c r="HA18" t="inlineStr"/>
       <c r="HB18" t="inlineStr"/>
+      <c r="HC18" t="inlineStr"/>
+      <c r="HD18" t="inlineStr"/>
+      <c r="HE18" t="inlineStr"/>
+      <c r="HF18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10285,6 +10373,10 @@
       <c r="GZ19" t="inlineStr"/>
       <c r="HA19" t="inlineStr"/>
       <c r="HB19" t="inlineStr"/>
+      <c r="HC19" t="inlineStr"/>
+      <c r="HD19" t="inlineStr"/>
+      <c r="HE19" t="inlineStr"/>
+      <c r="HF19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -10819,6 +10911,10 @@
       <c r="GZ20" t="inlineStr"/>
       <c r="HA20" t="inlineStr"/>
       <c r="HB20" t="inlineStr"/>
+      <c r="HC20" t="inlineStr"/>
+      <c r="HD20" t="inlineStr"/>
+      <c r="HE20" t="inlineStr"/>
+      <c r="HF20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11291,6 +11387,10 @@
       </c>
       <c r="HA21" t="inlineStr"/>
       <c r="HB21" t="inlineStr"/>
+      <c r="HC21" t="inlineStr"/>
+      <c r="HD21" t="inlineStr"/>
+      <c r="HE21" t="inlineStr"/>
+      <c r="HF21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -11639,6 +11739,1606 @@
           <t>7JVBu_U7W1AEd7dyoZ37wZOeelHewzgavOCk1lZNxA4</t>
         </is>
       </c>
+      <c r="HC22" t="inlineStr"/>
+      <c r="HD22" t="inlineStr"/>
+      <c r="HE22" t="inlineStr"/>
+      <c r="HF22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>240d36d7-83a8-4b67-bc49-05eb5a2caa78</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LV240721MWEA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-03-06 11:36:43</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2021-07-24</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Hindu</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>LV240721MWEA</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Upper</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>LV240721MWEA</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Jahnavi; Jahnavi</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>PHC</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr"/>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="inlineStr"/>
+      <c r="BI23" t="inlineStr"/>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr"/>
+      <c r="BM23" t="n">
+        <v>5555555000</v>
+      </c>
+      <c r="BN23" t="inlineStr"/>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>3-4/week</t>
+        </is>
+      </c>
+      <c r="BP23" t="inlineStr"/>
+      <c r="BQ23" t="inlineStr"/>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="BS23" t="inlineStr"/>
+      <c r="BT23" t="inlineStr">
+        <is>
+          <t>1-2/week</t>
+        </is>
+      </c>
+      <c r="BU23" t="inlineStr"/>
+      <c r="BV23" t="inlineStr"/>
+      <c r="BW23" t="inlineStr"/>
+      <c r="BX23" t="inlineStr"/>
+      <c r="BY23" t="inlineStr"/>
+      <c r="BZ23" t="inlineStr"/>
+      <c r="CA23" t="inlineStr"/>
+      <c r="CB23" t="inlineStr"/>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL23" t="inlineStr"/>
+      <c r="CM23" t="inlineStr"/>
+      <c r="CN23" t="inlineStr"/>
+      <c r="CO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CQ23" t="inlineStr"/>
+      <c r="CR23" t="inlineStr"/>
+      <c r="CS23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CT23" t="inlineStr"/>
+      <c r="CU23" t="inlineStr"/>
+      <c r="CV23" t="inlineStr"/>
+      <c r="CW23" t="inlineStr"/>
+      <c r="CX23" t="inlineStr">
+        <is>
+          <t>11:36:16</t>
+        </is>
+      </c>
+      <c r="CY23" t="inlineStr"/>
+      <c r="CZ23" t="inlineStr"/>
+      <c r="DA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB23" t="inlineStr"/>
+      <c r="DC23" t="inlineStr"/>
+      <c r="DD23" t="inlineStr"/>
+      <c r="DE23" t="inlineStr"/>
+      <c r="DF23" t="inlineStr"/>
+      <c r="DG23" t="inlineStr"/>
+      <c r="DH23" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="DI23" t="inlineStr">
+        <is>
+          <t>3-4/week</t>
+        </is>
+      </c>
+      <c r="DJ23" t="inlineStr"/>
+      <c r="DK23" t="inlineStr"/>
+      <c r="DL23" t="n">
+        <v>2</v>
+      </c>
+      <c r="DM23" t="inlineStr"/>
+      <c r="DN23" t="inlineStr">
+        <is>
+          <t>leo</t>
+        </is>
+      </c>
+      <c r="DO23" t="inlineStr"/>
+      <c r="DP23" t="inlineStr"/>
+      <c r="DQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR23" t="n">
+        <v>2</v>
+      </c>
+      <c r="DS23" t="inlineStr">
+        <is>
+          <t>11:36:09</t>
+        </is>
+      </c>
+      <c r="DT23" t="inlineStr"/>
+      <c r="DU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV23" t="inlineStr"/>
+      <c r="DW23" t="n">
+        <v>7</v>
+      </c>
+      <c r="DX23" t="inlineStr"/>
+      <c r="DY23" t="inlineStr"/>
+      <c r="DZ23" t="inlineStr"/>
+      <c r="EA23" t="inlineStr"/>
+      <c r="EB23" t="inlineStr"/>
+      <c r="EC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED23" t="inlineStr"/>
+      <c r="EE23" t="inlineStr"/>
+      <c r="EF23" t="inlineStr"/>
+      <c r="EG23" t="inlineStr"/>
+      <c r="EH23" t="inlineStr"/>
+      <c r="EI23" t="inlineStr"/>
+      <c r="EJ23" t="inlineStr"/>
+      <c r="EK23" t="n">
+        <v>1</v>
+      </c>
+      <c r="EL23" t="inlineStr"/>
+      <c r="EM23" t="inlineStr">
+        <is>
+          <t>west</t>
+        </is>
+      </c>
+      <c r="EN23" t="inlineStr"/>
+      <c r="EO23" t="inlineStr"/>
+      <c r="EP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER23" t="inlineStr"/>
+      <c r="ES23" t="inlineStr"/>
+      <c r="ET23" t="inlineStr"/>
+      <c r="EU23" t="inlineStr"/>
+      <c r="EV23" t="n">
+        <v>2</v>
+      </c>
+      <c r="EW23" t="inlineStr"/>
+      <c r="EX23" t="inlineStr"/>
+      <c r="EY23" t="inlineStr"/>
+      <c r="EZ23" t="inlineStr"/>
+      <c r="FA23" t="inlineStr"/>
+      <c r="FB23" t="inlineStr"/>
+      <c r="FC23" t="inlineStr">
+        <is>
+          <t>Jahnavi</t>
+        </is>
+      </c>
+      <c r="FD23" t="inlineStr"/>
+      <c r="FE23" t="inlineStr">
+        <is>
+          <t>2026-03-06T11:36:16+05:30</t>
+        </is>
+      </c>
+      <c r="FF23" t="n">
+        <v>120</v>
+      </c>
+      <c r="FG23" t="n">
+        <v>12</v>
+      </c>
+      <c r="FH23" t="inlineStr">
+        <is>
+          <t>4 years 7 months 10 days</t>
+        </is>
+      </c>
+      <c r="FI23" t="inlineStr">
+        <is>
+          <t>2026-03-06T11:34:29+05:30</t>
+        </is>
+      </c>
+      <c r="FJ23" t="inlineStr"/>
+      <c r="FK23" t="inlineStr"/>
+      <c r="FL23" t="inlineStr"/>
+      <c r="FM23" t="inlineStr"/>
+      <c r="FN23" t="inlineStr"/>
+      <c r="FO23" t="inlineStr"/>
+      <c r="FP23" t="inlineStr"/>
+      <c r="FQ23" t="inlineStr"/>
+      <c r="FR23" t="inlineStr"/>
+      <c r="FS23" t="inlineStr"/>
+      <c r="FT23" t="inlineStr"/>
+      <c r="FU23" t="inlineStr"/>
+      <c r="FV23" t="inlineStr"/>
+      <c r="FW23" t="inlineStr"/>
+      <c r="FX23" t="inlineStr"/>
+      <c r="FY23" t="inlineStr"/>
+      <c r="FZ23" t="inlineStr"/>
+      <c r="GA23" t="inlineStr"/>
+      <c r="GB23" t="inlineStr"/>
+      <c r="GC23" t="inlineStr"/>
+      <c r="GD23" t="inlineStr"/>
+      <c r="GE23" t="inlineStr"/>
+      <c r="GF23" t="inlineStr"/>
+      <c r="GG23" t="inlineStr"/>
+      <c r="GH23" t="inlineStr"/>
+      <c r="GI23" t="inlineStr"/>
+      <c r="GJ23" t="inlineStr"/>
+      <c r="GK23" t="inlineStr"/>
+      <c r="GL23" t="inlineStr"/>
+      <c r="GM23" t="inlineStr"/>
+      <c r="GN23" t="inlineStr"/>
+      <c r="GO23" t="inlineStr"/>
+      <c r="GP23" t="inlineStr"/>
+      <c r="GQ23" t="inlineStr"/>
+      <c r="GR23" t="inlineStr"/>
+      <c r="GS23" t="inlineStr"/>
+      <c r="GT23" t="inlineStr"/>
+      <c r="GU23" t="inlineStr"/>
+      <c r="GV23" t="inlineStr"/>
+      <c r="GW23" t="inlineStr"/>
+      <c r="GX23" t="inlineStr"/>
+      <c r="GY23" t="inlineStr"/>
+      <c r="GZ23" t="inlineStr"/>
+      <c r="HA23" t="inlineStr"/>
+      <c r="HB23" t="inlineStr"/>
+      <c r="HC23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="HD23" t="inlineStr">
+        <is>
+          <t>Non-invasive</t>
+        </is>
+      </c>
+      <c r="HE23" t="inlineStr">
+        <is>
+          <t>Masimo Rad-67</t>
+        </is>
+      </c>
+      <c r="HF23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3e4683eb-f06a-415a-9801-6cdb1c3f598e</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LV240721MWEA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-03-06 11:36:55</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2021-07-24</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Hindu</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>LV240721MWEA</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Upper</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>LV240721MWEA</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Jahnavi; Jahnavi; Jahnavi; Jahnavi</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>PHC</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr"/>
+      <c r="BA24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="inlineStr"/>
+      <c r="BH24" t="inlineStr"/>
+      <c r="BI24" t="inlineStr"/>
+      <c r="BJ24" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="BK24" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="BL24" t="inlineStr"/>
+      <c r="BM24" t="n">
+        <v>5555555000</v>
+      </c>
+      <c r="BN24" t="inlineStr"/>
+      <c r="BO24" t="inlineStr">
+        <is>
+          <t>3-4/week</t>
+        </is>
+      </c>
+      <c r="BP24" t="inlineStr"/>
+      <c r="BQ24" t="inlineStr"/>
+      <c r="BR24" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="BS24" t="inlineStr"/>
+      <c r="BT24" t="inlineStr">
+        <is>
+          <t>1-2/week</t>
+        </is>
+      </c>
+      <c r="BU24" t="inlineStr"/>
+      <c r="BV24" t="inlineStr"/>
+      <c r="BW24" t="inlineStr"/>
+      <c r="BX24" t="inlineStr"/>
+      <c r="BY24" t="inlineStr"/>
+      <c r="BZ24" t="inlineStr"/>
+      <c r="CA24" t="inlineStr"/>
+      <c r="CB24" t="inlineStr"/>
+      <c r="CC24" t="inlineStr"/>
+      <c r="CD24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CE24" t="inlineStr"/>
+      <c r="CF24" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="CG24" t="inlineStr"/>
+      <c r="CH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI24" t="inlineStr"/>
+      <c r="CJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL24" t="inlineStr"/>
+      <c r="CM24" t="inlineStr"/>
+      <c r="CN24" t="inlineStr"/>
+      <c r="CO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CQ24" t="inlineStr"/>
+      <c r="CR24" t="inlineStr"/>
+      <c r="CS24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CT24" t="inlineStr"/>
+      <c r="CU24" t="inlineStr"/>
+      <c r="CV24" t="inlineStr"/>
+      <c r="CW24" t="inlineStr"/>
+      <c r="CX24" t="inlineStr">
+        <is>
+          <t>11:36:16</t>
+        </is>
+      </c>
+      <c r="CY24" t="inlineStr"/>
+      <c r="CZ24" t="inlineStr"/>
+      <c r="DA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB24" t="inlineStr"/>
+      <c r="DC24" t="inlineStr"/>
+      <c r="DD24" t="inlineStr"/>
+      <c r="DE24" t="inlineStr"/>
+      <c r="DF24" t="inlineStr"/>
+      <c r="DG24" t="inlineStr"/>
+      <c r="DH24" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="DI24" t="inlineStr">
+        <is>
+          <t>3-4/week</t>
+        </is>
+      </c>
+      <c r="DJ24" t="inlineStr"/>
+      <c r="DK24" t="inlineStr"/>
+      <c r="DL24" t="n">
+        <v>2</v>
+      </c>
+      <c r="DM24" t="inlineStr"/>
+      <c r="DN24" t="inlineStr">
+        <is>
+          <t>leo</t>
+        </is>
+      </c>
+      <c r="DO24" t="inlineStr"/>
+      <c r="DP24" t="inlineStr"/>
+      <c r="DQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR24" t="n">
+        <v>2</v>
+      </c>
+      <c r="DS24" t="inlineStr">
+        <is>
+          <t>11:36:09</t>
+        </is>
+      </c>
+      <c r="DT24" t="inlineStr"/>
+      <c r="DU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV24" t="inlineStr"/>
+      <c r="DW24" t="n">
+        <v>7</v>
+      </c>
+      <c r="DX24" t="inlineStr"/>
+      <c r="DY24" t="inlineStr"/>
+      <c r="DZ24" t="inlineStr"/>
+      <c r="EA24" t="inlineStr"/>
+      <c r="EB24" t="inlineStr"/>
+      <c r="EC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED24" t="inlineStr"/>
+      <c r="EE24" t="inlineStr"/>
+      <c r="EF24" t="inlineStr"/>
+      <c r="EG24" t="inlineStr"/>
+      <c r="EH24" t="inlineStr"/>
+      <c r="EI24" t="inlineStr"/>
+      <c r="EJ24" t="inlineStr"/>
+      <c r="EK24" t="n">
+        <v>1</v>
+      </c>
+      <c r="EL24" t="inlineStr"/>
+      <c r="EM24" t="inlineStr">
+        <is>
+          <t>west</t>
+        </is>
+      </c>
+      <c r="EN24" t="inlineStr"/>
+      <c r="EO24" t="inlineStr"/>
+      <c r="EP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER24" t="inlineStr"/>
+      <c r="ES24" t="inlineStr"/>
+      <c r="ET24" t="inlineStr"/>
+      <c r="EU24" t="inlineStr"/>
+      <c r="EV24" t="n">
+        <v>2</v>
+      </c>
+      <c r="EW24" t="inlineStr"/>
+      <c r="EX24" t="inlineStr"/>
+      <c r="EY24" t="inlineStr"/>
+      <c r="EZ24" t="inlineStr"/>
+      <c r="FA24" t="inlineStr"/>
+      <c r="FB24" t="inlineStr"/>
+      <c r="FC24" t="inlineStr">
+        <is>
+          <t>Jahnavi</t>
+        </is>
+      </c>
+      <c r="FD24" t="inlineStr"/>
+      <c r="FE24" t="inlineStr">
+        <is>
+          <t>2026-03-06T11:36:16+05:30</t>
+        </is>
+      </c>
+      <c r="FF24" t="n">
+        <v>120</v>
+      </c>
+      <c r="FG24" t="n">
+        <v>12</v>
+      </c>
+      <c r="FH24" t="inlineStr">
+        <is>
+          <t>4 years 7 months 10 days</t>
+        </is>
+      </c>
+      <c r="FI24" t="inlineStr">
+        <is>
+          <t>2026-03-06T11:36:44+05:30</t>
+        </is>
+      </c>
+      <c r="FJ24" t="inlineStr"/>
+      <c r="FK24" t="inlineStr"/>
+      <c r="FL24" t="inlineStr"/>
+      <c r="FM24" t="inlineStr"/>
+      <c r="FN24" t="inlineStr"/>
+      <c r="FO24" t="inlineStr"/>
+      <c r="FP24" t="inlineStr"/>
+      <c r="FQ24" t="inlineStr"/>
+      <c r="FR24" t="inlineStr"/>
+      <c r="FS24" t="inlineStr"/>
+      <c r="FT24" t="inlineStr"/>
+      <c r="FU24" t="inlineStr"/>
+      <c r="FV24" t="inlineStr"/>
+      <c r="FW24" t="inlineStr"/>
+      <c r="FX24" t="inlineStr"/>
+      <c r="FY24" t="inlineStr"/>
+      <c r="FZ24" t="inlineStr"/>
+      <c r="GA24" t="inlineStr"/>
+      <c r="GB24" t="inlineStr"/>
+      <c r="GC24" t="inlineStr"/>
+      <c r="GD24" t="inlineStr"/>
+      <c r="GE24" t="inlineStr"/>
+      <c r="GF24" t="inlineStr"/>
+      <c r="GG24" t="inlineStr"/>
+      <c r="GH24" t="inlineStr"/>
+      <c r="GI24" t="inlineStr"/>
+      <c r="GJ24" t="inlineStr"/>
+      <c r="GK24" t="inlineStr"/>
+      <c r="GL24" t="inlineStr"/>
+      <c r="GM24" t="inlineStr"/>
+      <c r="GN24" t="inlineStr"/>
+      <c r="GO24" t="inlineStr"/>
+      <c r="GP24" t="inlineStr"/>
+      <c r="GQ24" t="inlineStr"/>
+      <c r="GR24" t="inlineStr"/>
+      <c r="GS24" t="inlineStr"/>
+      <c r="GT24" t="inlineStr"/>
+      <c r="GU24" t="inlineStr"/>
+      <c r="GV24" t="inlineStr"/>
+      <c r="GW24" t="inlineStr"/>
+      <c r="GX24" t="inlineStr"/>
+      <c r="GY24" t="inlineStr"/>
+      <c r="GZ24" t="inlineStr"/>
+      <c r="HA24" t="inlineStr"/>
+      <c r="HB24" t="inlineStr"/>
+      <c r="HC24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="HD24" t="inlineStr">
+        <is>
+          <t>Non-invasive</t>
+        </is>
+      </c>
+      <c r="HE24" t="inlineStr">
+        <is>
+          <t>Masimo Rad-67</t>
+        </is>
+      </c>
+      <c r="HF24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>02726c43-42e1-4299-b1ad-4a38a5d9abd4</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LV240721MWEA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-03-07 14:15:08</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2021-07-24</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>LV240721MWEA</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Upper</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>LV240721MWEA</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Jahnavi</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr"/>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="inlineStr"/>
+      <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr"/>
+      <c r="BJ25" t="inlineStr"/>
+      <c r="BK25" t="inlineStr"/>
+      <c r="BL25" t="inlineStr"/>
+      <c r="BM25" t="inlineStr"/>
+      <c r="BN25" t="inlineStr"/>
+      <c r="BO25" t="inlineStr"/>
+      <c r="BP25" t="inlineStr"/>
+      <c r="BQ25" t="inlineStr"/>
+      <c r="BR25" t="inlineStr"/>
+      <c r="BS25" t="inlineStr"/>
+      <c r="BT25" t="inlineStr"/>
+      <c r="BU25" t="inlineStr"/>
+      <c r="BV25" t="inlineStr"/>
+      <c r="BW25" t="inlineStr"/>
+      <c r="BX25" t="inlineStr"/>
+      <c r="BY25" t="inlineStr"/>
+      <c r="BZ25" t="inlineStr"/>
+      <c r="CA25" t="inlineStr"/>
+      <c r="CB25" t="inlineStr"/>
+      <c r="CC25" t="inlineStr"/>
+      <c r="CD25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CE25" t="inlineStr"/>
+      <c r="CF25" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="CG25" t="inlineStr"/>
+      <c r="CH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI25" t="inlineStr"/>
+      <c r="CJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL25" t="inlineStr"/>
+      <c r="CM25" t="inlineStr"/>
+      <c r="CN25" t="inlineStr"/>
+      <c r="CO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CQ25" t="inlineStr"/>
+      <c r="CR25" t="inlineStr"/>
+      <c r="CS25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CT25" t="inlineStr"/>
+      <c r="CU25" t="inlineStr"/>
+      <c r="CV25" t="inlineStr"/>
+      <c r="CW25" t="inlineStr"/>
+      <c r="CX25" t="inlineStr"/>
+      <c r="CY25" t="inlineStr"/>
+      <c r="CZ25" t="inlineStr"/>
+      <c r="DA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB25" t="inlineStr"/>
+      <c r="DC25" t="inlineStr"/>
+      <c r="DD25" t="inlineStr"/>
+      <c r="DE25" t="inlineStr"/>
+      <c r="DF25" t="inlineStr"/>
+      <c r="DG25" t="inlineStr"/>
+      <c r="DH25" t="inlineStr"/>
+      <c r="DI25" t="inlineStr"/>
+      <c r="DJ25" t="inlineStr"/>
+      <c r="DK25" t="inlineStr"/>
+      <c r="DL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM25" t="inlineStr"/>
+      <c r="DN25" t="inlineStr">
+        <is>
+          <t>leo</t>
+        </is>
+      </c>
+      <c r="DO25" t="inlineStr"/>
+      <c r="DP25" t="inlineStr"/>
+      <c r="DQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS25" t="inlineStr"/>
+      <c r="DT25" t="inlineStr"/>
+      <c r="DU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV25" t="inlineStr"/>
+      <c r="DW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX25" t="inlineStr"/>
+      <c r="DY25" t="inlineStr"/>
+      <c r="DZ25" t="inlineStr"/>
+      <c r="EA25" t="inlineStr"/>
+      <c r="EB25" t="inlineStr"/>
+      <c r="EC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED25" t="inlineStr"/>
+      <c r="EE25" t="inlineStr"/>
+      <c r="EF25" t="inlineStr"/>
+      <c r="EG25" t="inlineStr"/>
+      <c r="EH25" t="inlineStr"/>
+      <c r="EI25" t="inlineStr"/>
+      <c r="EJ25" t="inlineStr"/>
+      <c r="EK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL25" t="inlineStr"/>
+      <c r="EM25" t="inlineStr">
+        <is>
+          <t>west</t>
+        </is>
+      </c>
+      <c r="EN25" t="inlineStr"/>
+      <c r="EO25" t="inlineStr"/>
+      <c r="EP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER25" t="inlineStr"/>
+      <c r="ES25" t="inlineStr"/>
+      <c r="ET25" t="inlineStr"/>
+      <c r="EU25" t="inlineStr"/>
+      <c r="EV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW25" t="inlineStr"/>
+      <c r="EX25" t="inlineStr"/>
+      <c r="EY25" t="inlineStr"/>
+      <c r="EZ25" t="inlineStr"/>
+      <c r="FA25" t="inlineStr"/>
+      <c r="FB25" t="inlineStr"/>
+      <c r="FC25" t="inlineStr">
+        <is>
+          <t>Jahnavi</t>
+        </is>
+      </c>
+      <c r="FD25" t="inlineStr"/>
+      <c r="FE25" t="inlineStr">
+        <is>
+          <t>2026-03-07T14:14:31+05:30</t>
+        </is>
+      </c>
+      <c r="FF25" t="inlineStr"/>
+      <c r="FG25" t="inlineStr"/>
+      <c r="FH25" t="inlineStr">
+        <is>
+          <t>4 years 7 months 11 days</t>
+        </is>
+      </c>
+      <c r="FI25" t="inlineStr">
+        <is>
+          <t>2026-03-07T14:14:31+05:30</t>
+        </is>
+      </c>
+      <c r="FJ25" t="inlineStr"/>
+      <c r="FK25" t="inlineStr"/>
+      <c r="FL25" t="inlineStr"/>
+      <c r="FM25" t="inlineStr"/>
+      <c r="FN25" t="inlineStr"/>
+      <c r="FO25" t="inlineStr"/>
+      <c r="FP25" t="inlineStr"/>
+      <c r="FQ25" t="inlineStr"/>
+      <c r="FR25" t="inlineStr"/>
+      <c r="FS25" t="inlineStr"/>
+      <c r="FT25" t="inlineStr"/>
+      <c r="FU25" t="inlineStr"/>
+      <c r="FV25" t="inlineStr"/>
+      <c r="FW25" t="inlineStr"/>
+      <c r="FX25" t="inlineStr"/>
+      <c r="FY25" t="inlineStr"/>
+      <c r="FZ25" t="inlineStr"/>
+      <c r="GA25" t="inlineStr"/>
+      <c r="GB25" t="inlineStr"/>
+      <c r="GC25" t="inlineStr"/>
+      <c r="GD25" t="inlineStr"/>
+      <c r="GE25" t="inlineStr"/>
+      <c r="GF25" t="inlineStr"/>
+      <c r="GG25" t="inlineStr"/>
+      <c r="GH25" t="inlineStr"/>
+      <c r="GI25" t="inlineStr"/>
+      <c r="GJ25" t="inlineStr"/>
+      <c r="GK25" t="inlineStr"/>
+      <c r="GL25" t="inlineStr"/>
+      <c r="GM25" t="inlineStr"/>
+      <c r="GN25" t="inlineStr"/>
+      <c r="GO25" t="inlineStr"/>
+      <c r="GP25" t="inlineStr"/>
+      <c r="GQ25" t="inlineStr"/>
+      <c r="GR25" t="inlineStr"/>
+      <c r="GS25" t="inlineStr"/>
+      <c r="GT25" t="inlineStr"/>
+      <c r="GU25" t="inlineStr"/>
+      <c r="GV25" t="inlineStr"/>
+      <c r="GW25" t="inlineStr"/>
+      <c r="GX25" t="inlineStr"/>
+      <c r="GY25" t="inlineStr"/>
+      <c r="GZ25" t="inlineStr"/>
+      <c r="HA25" t="inlineStr"/>
+      <c r="HB25" t="inlineStr"/>
+      <c r="HC25" t="inlineStr"/>
+      <c r="HD25" t="inlineStr"/>
+      <c r="HE25" t="inlineStr"/>
+      <c r="HF25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>5679a6b1-398d-4ffe-b592-d0a95d29b834</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LV240721MWEA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-03-07 14:16:08</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2021-07-24</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>LV240721MWEA</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Upper</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>LV240721MWEA</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>praneeth</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="n">
+        <v>29</v>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr"/>
+      <c r="BA26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="inlineStr"/>
+      <c r="BG26" t="inlineStr"/>
+      <c r="BH26" t="inlineStr"/>
+      <c r="BI26" t="inlineStr"/>
+      <c r="BJ26" t="inlineStr"/>
+      <c r="BK26" t="inlineStr"/>
+      <c r="BL26" t="inlineStr"/>
+      <c r="BM26" t="inlineStr"/>
+      <c r="BN26" t="inlineStr"/>
+      <c r="BO26" t="inlineStr"/>
+      <c r="BP26" t="inlineStr"/>
+      <c r="BQ26" t="inlineStr"/>
+      <c r="BR26" t="inlineStr"/>
+      <c r="BS26" t="inlineStr"/>
+      <c r="BT26" t="inlineStr"/>
+      <c r="BU26" t="inlineStr"/>
+      <c r="BV26" t="inlineStr"/>
+      <c r="BW26" t="inlineStr"/>
+      <c r="BX26" t="inlineStr"/>
+      <c r="BY26" t="inlineStr"/>
+      <c r="BZ26" t="inlineStr"/>
+      <c r="CA26" t="inlineStr"/>
+      <c r="CB26" t="inlineStr"/>
+      <c r="CC26" t="inlineStr"/>
+      <c r="CD26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CE26" t="inlineStr"/>
+      <c r="CF26" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="CG26" t="inlineStr"/>
+      <c r="CH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI26" t="inlineStr"/>
+      <c r="CJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL26" t="inlineStr"/>
+      <c r="CM26" t="inlineStr"/>
+      <c r="CN26" t="inlineStr"/>
+      <c r="CO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CQ26" t="inlineStr"/>
+      <c r="CR26" t="inlineStr"/>
+      <c r="CS26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CT26" t="inlineStr"/>
+      <c r="CU26" t="inlineStr"/>
+      <c r="CV26" t="inlineStr"/>
+      <c r="CW26" t="inlineStr"/>
+      <c r="CX26" t="inlineStr"/>
+      <c r="CY26" t="inlineStr"/>
+      <c r="CZ26" t="inlineStr"/>
+      <c r="DA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB26" t="inlineStr"/>
+      <c r="DC26" t="inlineStr"/>
+      <c r="DD26" t="inlineStr"/>
+      <c r="DE26" t="inlineStr"/>
+      <c r="DF26" t="inlineStr"/>
+      <c r="DG26" t="inlineStr"/>
+      <c r="DH26" t="inlineStr"/>
+      <c r="DI26" t="inlineStr"/>
+      <c r="DJ26" t="inlineStr"/>
+      <c r="DK26" t="inlineStr"/>
+      <c r="DL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM26" t="inlineStr"/>
+      <c r="DN26" t="inlineStr">
+        <is>
+          <t>leo</t>
+        </is>
+      </c>
+      <c r="DO26" t="inlineStr"/>
+      <c r="DP26" t="inlineStr"/>
+      <c r="DQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS26" t="inlineStr"/>
+      <c r="DT26" t="inlineStr"/>
+      <c r="DU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV26" t="inlineStr"/>
+      <c r="DW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX26" t="inlineStr"/>
+      <c r="DY26" t="inlineStr"/>
+      <c r="DZ26" t="inlineStr"/>
+      <c r="EA26" t="inlineStr"/>
+      <c r="EB26" t="inlineStr"/>
+      <c r="EC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED26" t="inlineStr"/>
+      <c r="EE26" t="inlineStr"/>
+      <c r="EF26" t="inlineStr"/>
+      <c r="EG26" t="inlineStr"/>
+      <c r="EH26" t="inlineStr"/>
+      <c r="EI26" t="inlineStr"/>
+      <c r="EJ26" t="inlineStr"/>
+      <c r="EK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL26" t="inlineStr"/>
+      <c r="EM26" t="inlineStr">
+        <is>
+          <t>west</t>
+        </is>
+      </c>
+      <c r="EN26" t="inlineStr"/>
+      <c r="EO26" t="inlineStr"/>
+      <c r="EP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER26" t="inlineStr"/>
+      <c r="ES26" t="inlineStr"/>
+      <c r="ET26" t="inlineStr"/>
+      <c r="EU26" t="inlineStr"/>
+      <c r="EV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW26" t="inlineStr"/>
+      <c r="EX26" t="inlineStr"/>
+      <c r="EY26" t="inlineStr"/>
+      <c r="EZ26" t="inlineStr"/>
+      <c r="FA26" t="inlineStr"/>
+      <c r="FB26" t="inlineStr"/>
+      <c r="FC26" t="inlineStr">
+        <is>
+          <t>Jahnavi</t>
+        </is>
+      </c>
+      <c r="FD26" t="inlineStr"/>
+      <c r="FE26" t="inlineStr">
+        <is>
+          <t>2026-03-07T14:15:10+05:30</t>
+        </is>
+      </c>
+      <c r="FF26" t="n">
+        <v>12</v>
+      </c>
+      <c r="FG26" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="FH26" t="inlineStr">
+        <is>
+          <t>4 years 7 months 11 days</t>
+        </is>
+      </c>
+      <c r="FI26" t="inlineStr">
+        <is>
+          <t>2026-03-07T14:15:10+05:30</t>
+        </is>
+      </c>
+      <c r="FJ26" t="inlineStr"/>
+      <c r="FK26" t="inlineStr"/>
+      <c r="FL26" t="inlineStr"/>
+      <c r="FM26" t="inlineStr"/>
+      <c r="FN26" t="inlineStr"/>
+      <c r="FO26" t="inlineStr"/>
+      <c r="FP26" t="inlineStr"/>
+      <c r="FQ26" t="inlineStr"/>
+      <c r="FR26" t="inlineStr"/>
+      <c r="FS26" t="inlineStr"/>
+      <c r="FT26" t="inlineStr"/>
+      <c r="FU26" t="inlineStr"/>
+      <c r="FV26" t="inlineStr"/>
+      <c r="FW26" t="inlineStr"/>
+      <c r="FX26" t="inlineStr"/>
+      <c r="FY26" t="inlineStr"/>
+      <c r="FZ26" t="inlineStr"/>
+      <c r="GA26" t="inlineStr"/>
+      <c r="GB26" t="inlineStr"/>
+      <c r="GC26" t="inlineStr"/>
+      <c r="GD26" t="inlineStr"/>
+      <c r="GE26" t="inlineStr"/>
+      <c r="GF26" t="inlineStr"/>
+      <c r="GG26" t="inlineStr"/>
+      <c r="GH26" t="inlineStr"/>
+      <c r="GI26" t="inlineStr"/>
+      <c r="GJ26" t="inlineStr"/>
+      <c r="GK26" t="inlineStr"/>
+      <c r="GL26" t="inlineStr"/>
+      <c r="GM26" t="inlineStr"/>
+      <c r="GN26" t="inlineStr"/>
+      <c r="GO26" t="inlineStr"/>
+      <c r="GP26" t="inlineStr"/>
+      <c r="GQ26" t="inlineStr"/>
+      <c r="GR26" t="inlineStr"/>
+      <c r="GS26" t="inlineStr"/>
+      <c r="GT26" t="inlineStr"/>
+      <c r="GU26" t="inlineStr"/>
+      <c r="GV26" t="inlineStr"/>
+      <c r="GW26" t="inlineStr"/>
+      <c r="GX26" t="inlineStr"/>
+      <c r="GY26" t="inlineStr"/>
+      <c r="GZ26" t="inlineStr"/>
+      <c r="HA26" t="inlineStr"/>
+      <c r="HB26" t="inlineStr"/>
+      <c r="HC26" t="inlineStr"/>
+      <c r="HD26" t="inlineStr"/>
+      <c r="HE26" t="inlineStr"/>
+      <c r="HF26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/responses.xlsx
+++ b/responses.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Responses" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
